--- a/Fig.3(a).xlsx
+++ b/Fig.3(a).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -413,7 +413,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>3.35028E-5</v>
+        <v>0</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -438,8 +438,8 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1.17E-3</v>
+      <c r="A8" s="1">
+        <v>4.4670300000000001E-4</v>
       </c>
       <c r="B8">
         <v>1.5625</v>
@@ -451,7 +451,7 @@
         <v>1.5625</v>
       </c>
       <c r="E8" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>1.5625</v>
@@ -465,13 +465,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2.7200000000000002E-3</v>
+        <v>1.1800000000000001E-3</v>
       </c>
       <c r="B9">
         <v>3.125</v>
       </c>
       <c r="C9" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>3.125</v>
@@ -491,13 +491,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>4.6699999999999997E-3</v>
+        <v>2.32E-3</v>
       </c>
       <c r="B10">
         <v>4.6875</v>
       </c>
       <c r="C10" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>4.6875</v>
@@ -517,19 +517,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>7.0699999999999999E-3</v>
+        <v>4.0699999999999998E-3</v>
       </c>
       <c r="B11">
         <v>6.25</v>
       </c>
       <c r="C11" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>6.25</v>
       </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="E11" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F11">
         <v>6.25</v>
@@ -543,13 +543,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9.6699999999999998E-3</v>
+        <v>6.43E-3</v>
       </c>
       <c r="B12">
         <v>7.8125</v>
       </c>
       <c r="C12" s="1">
-        <v>3.35028E-5</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>7.8125</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1.2030000000000001E-2</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="B13">
         <v>9.375</v>
       </c>
       <c r="C13">
-        <v>1.1900000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>9.375</v>
@@ -595,13 +595,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1.4120000000000001E-2</v>
+        <v>1.354E-2</v>
       </c>
       <c r="B14">
         <v>10.9375</v>
       </c>
       <c r="C14">
-        <v>7.9699999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>10.9375</v>
@@ -621,13 +621,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1.6160000000000001E-2</v>
+        <v>1.6389999999999998E-2</v>
       </c>
       <c r="B15">
         <v>12.5</v>
       </c>
       <c r="C15">
-        <v>1.423E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>12.5</v>
@@ -647,19 +647,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1.823E-2</v>
+        <v>1.848E-2</v>
       </c>
       <c r="B16">
         <v>14.0625</v>
       </c>
       <c r="C16">
-        <v>1.814E-2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>14.0625</v>
       </c>
-      <c r="E16">
-        <v>0</v>
+      <c r="E16" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F16">
         <v>14.0625</v>
@@ -673,13 +673,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2.026E-2</v>
+        <v>2.0539999999999999E-2</v>
       </c>
       <c r="B17">
         <v>15.625</v>
       </c>
       <c r="C17">
-        <v>2.027E-2</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>15.625</v>
@@ -699,13 +699,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2.231E-2</v>
+        <v>2.2579999999999999E-2</v>
       </c>
       <c r="B18">
         <v>17.1875</v>
       </c>
       <c r="C18">
-        <v>2.232E-2</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>17.1875</v>
@@ -725,19 +725,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2.436E-2</v>
+        <v>2.462E-2</v>
       </c>
       <c r="B19">
         <v>18.75</v>
       </c>
       <c r="C19">
-        <v>2.4369999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>18.75</v>
       </c>
       <c r="E19">
-        <v>2.5500000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>18.75</v>
@@ -751,19 +751,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2.64E-2</v>
+        <v>2.6669999999999999E-2</v>
       </c>
       <c r="B20">
         <v>20.3125</v>
       </c>
       <c r="C20">
-        <v>2.6409999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>20.3125</v>
       </c>
       <c r="E20">
-        <v>2.6100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>20.3125</v>
@@ -777,19 +777,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2.844E-2</v>
+        <v>2.8719999999999999E-2</v>
       </c>
       <c r="B21">
         <v>21.875</v>
       </c>
       <c r="C21">
-        <v>2.8469999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>21.875</v>
       </c>
       <c r="E21">
-        <v>2.8389999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>21.875</v>
@@ -803,25 +803,25 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3.0499999999999999E-2</v>
+        <v>3.0769999999999999E-2</v>
       </c>
       <c r="B22">
         <v>23.4375</v>
       </c>
       <c r="C22">
-        <v>3.0509999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>23.4375</v>
       </c>
       <c r="E22">
-        <v>3.0439999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>23.4375</v>
       </c>
       <c r="G22">
-        <v>8.8100000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>23.4375</v>
@@ -829,25 +829,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3.2539999999999999E-2</v>
+        <v>3.2809999999999999E-2</v>
       </c>
       <c r="B23">
         <v>25</v>
       </c>
       <c r="C23">
-        <v>3.2550000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>25</v>
       </c>
       <c r="E23">
-        <v>3.2489999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>25</v>
       </c>
       <c r="G23">
-        <v>3.245E-2</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>25</v>
@@ -855,25 +855,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>3.4590000000000003E-2</v>
+        <v>3.4849999999999999E-2</v>
       </c>
       <c r="B24">
         <v>26.5625</v>
       </c>
       <c r="C24">
-        <v>3.4599999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>26.5625</v>
       </c>
       <c r="E24">
-        <v>3.4520000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>26.5625</v>
       </c>
       <c r="G24">
-        <v>3.4500000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>26.5625</v>
@@ -881,25 +881,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3.662E-2</v>
+        <v>3.6900000000000002E-2</v>
       </c>
       <c r="B25">
         <v>28.125</v>
       </c>
       <c r="C25">
-        <v>3.6639999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>28.125</v>
       </c>
       <c r="E25">
-        <v>3.6560000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>28.125</v>
       </c>
       <c r="G25">
-        <v>3.6540000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>28.125</v>
@@ -907,25 +907,25 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>3.8670000000000003E-2</v>
+        <v>3.8949999999999999E-2</v>
       </c>
       <c r="B26">
         <v>29.6875</v>
       </c>
       <c r="C26">
-        <v>3.8699999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>29.6875</v>
       </c>
       <c r="E26">
-        <v>3.8620000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>29.6875</v>
       </c>
       <c r="G26">
-        <v>3.8600000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>29.6875</v>
@@ -933,25 +933,25 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4.0719999999999999E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="B27">
         <v>31.25</v>
       </c>
       <c r="C27">
-        <v>4.0730000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>31.25</v>
       </c>
       <c r="E27">
-        <v>4.0660000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>31.25</v>
       </c>
-      <c r="G27">
-        <v>4.0640000000000003E-2</v>
+      <c r="G27" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="H27">
         <v>31.25</v>
@@ -959,25 +959,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4.2759999999999999E-2</v>
+        <v>4.3029999999999999E-2</v>
       </c>
       <c r="B28">
         <v>32.8125</v>
       </c>
       <c r="C28">
-        <v>4.2770000000000002E-2</v>
+        <v>4.3029999999999999E-2</v>
       </c>
       <c r="D28">
         <v>32.8125</v>
       </c>
       <c r="E28">
-        <v>4.2689999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>32.8125</v>
       </c>
       <c r="G28">
-        <v>4.267E-2</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>32.8125</v>
@@ -985,25 +985,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4.48E-2</v>
+        <v>4.5080000000000002E-2</v>
       </c>
       <c r="B29">
         <v>34.375</v>
       </c>
       <c r="C29">
-        <v>4.4819999999999999E-2</v>
+        <v>4.5080000000000002E-2</v>
       </c>
       <c r="D29">
         <v>34.375</v>
       </c>
       <c r="E29">
-        <v>4.4729999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>34.375</v>
       </c>
       <c r="G29">
-        <v>4.4699999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>34.375</v>
@@ -1011,25 +1011,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4.6859999999999999E-2</v>
+        <v>4.7129999999999998E-2</v>
       </c>
       <c r="B30">
         <v>35.9375</v>
       </c>
       <c r="C30">
-        <v>4.6870000000000002E-2</v>
+        <v>4.7129999999999998E-2</v>
       </c>
       <c r="D30">
         <v>35.9375</v>
       </c>
       <c r="E30">
-        <v>4.6780000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>35.9375</v>
       </c>
       <c r="G30">
-        <v>4.6760000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>35.9375</v>
@@ -1037,25 +1037,25 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4.8899999999999999E-2</v>
+        <v>4.9180000000000001E-2</v>
       </c>
       <c r="B31">
         <v>37.5</v>
       </c>
       <c r="C31">
-        <v>4.8899999999999999E-2</v>
+        <v>4.9180000000000001E-2</v>
       </c>
       <c r="D31">
         <v>37.5</v>
       </c>
       <c r="E31">
-        <v>4.8820000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>37.5</v>
       </c>
       <c r="G31">
-        <v>4.8800000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>37.5</v>
@@ -1063,25 +1063,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>5.0959999999999998E-2</v>
+        <v>5.1229999999999998E-2</v>
       </c>
       <c r="B32">
         <v>39.0625</v>
       </c>
       <c r="C32">
-        <v>5.0970000000000001E-2</v>
+        <v>5.1229999999999998E-2</v>
       </c>
       <c r="D32">
         <v>39.0625</v>
       </c>
       <c r="E32">
-        <v>5.0889999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>39.0625</v>
       </c>
       <c r="G32">
-        <v>5.0860000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>39.0625</v>
@@ -1089,25 +1089,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5.2999999999999999E-2</v>
+        <v>5.3280000000000001E-2</v>
       </c>
       <c r="B33">
         <v>40.625</v>
       </c>
       <c r="C33">
-        <v>5.3010000000000002E-2</v>
+        <v>5.3280000000000001E-2</v>
       </c>
       <c r="D33">
         <v>40.625</v>
       </c>
       <c r="E33">
-        <v>5.2920000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>40.625</v>
       </c>
       <c r="G33">
-        <v>5.289E-2</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>40.625</v>
@@ -1115,25 +1115,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>5.5050000000000002E-2</v>
+        <v>5.5320000000000001E-2</v>
       </c>
       <c r="B34">
         <v>42.1875</v>
       </c>
       <c r="C34">
-        <v>5.5070000000000001E-2</v>
+        <v>5.5320000000000001E-2</v>
       </c>
       <c r="D34">
         <v>42.1875</v>
       </c>
       <c r="E34">
-        <v>5.4980000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>42.1875</v>
       </c>
       <c r="G34">
-        <v>5.4940000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>42.1875</v>
@@ -1141,25 +1141,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>5.7090000000000002E-2</v>
+        <v>5.7369999999999997E-2</v>
       </c>
       <c r="B35">
         <v>43.75</v>
       </c>
       <c r="C35">
-        <v>5.7110000000000001E-2</v>
+        <v>5.7360000000000001E-2</v>
       </c>
       <c r="D35">
         <v>43.75</v>
       </c>
       <c r="E35">
-        <v>5.7009999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>43.75</v>
       </c>
       <c r="G35">
-        <v>5.6980000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>43.75</v>
@@ -1167,25 +1167,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5.9130000000000002E-2</v>
+        <v>5.9409999999999998E-2</v>
       </c>
       <c r="B36">
         <v>45.3125</v>
       </c>
       <c r="C36">
-        <v>5.9139999999999998E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="D36">
         <v>45.3125</v>
       </c>
       <c r="E36">
-        <v>5.9049999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>45.3125</v>
       </c>
       <c r="G36">
-        <v>5.901E-2</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>45.3125</v>
@@ -1193,25 +1193,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>6.1179999999999998E-2</v>
+        <v>6.1469999999999997E-2</v>
       </c>
       <c r="B37">
         <v>46.875</v>
       </c>
       <c r="C37">
-        <v>6.1199999999999997E-2</v>
+        <v>6.1460000000000001E-2</v>
       </c>
       <c r="D37">
         <v>46.875</v>
       </c>
       <c r="E37">
-        <v>6.1100000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>46.875</v>
       </c>
       <c r="G37">
-        <v>6.105E-2</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>46.875</v>
@@ -1219,25 +1219,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>6.3229999999999995E-2</v>
+        <v>6.3509999999999997E-2</v>
       </c>
       <c r="B38">
         <v>48.4375</v>
       </c>
       <c r="C38">
-        <v>6.3250000000000001E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="D38">
         <v>48.4375</v>
       </c>
       <c r="E38">
-        <v>6.3149999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>48.4375</v>
       </c>
       <c r="G38">
-        <v>6.3109999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>48.4375</v>
@@ -1245,25 +1245,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6.5269999999999995E-2</v>
+        <v>6.5619999999999998E-2</v>
       </c>
       <c r="B39">
         <v>50</v>
       </c>
       <c r="C39">
-        <v>6.5299999999999997E-2</v>
+        <v>6.5619999999999998E-2</v>
       </c>
       <c r="D39">
         <v>50</v>
       </c>
       <c r="E39">
-        <v>6.5199999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>50</v>
       </c>
       <c r="G39">
-        <v>6.5140000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>50</v>
@@ -1271,25 +1271,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>6.7400000000000002E-2</v>
+        <v>6.7659999999999998E-2</v>
       </c>
       <c r="B40">
         <v>51.5625</v>
       </c>
       <c r="C40">
-        <v>6.7419999999999994E-2</v>
+        <v>6.7650000000000002E-2</v>
       </c>
       <c r="D40">
         <v>51.5625</v>
       </c>
       <c r="E40">
-        <v>6.7309999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>51.5625</v>
       </c>
       <c r="G40">
-        <v>6.7250000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>51.5625</v>
@@ -1297,25 +1297,25 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>6.9430000000000006E-2</v>
+        <v>6.9720000000000004E-2</v>
       </c>
       <c r="B41">
         <v>53.125</v>
       </c>
       <c r="C41">
-        <v>6.9440000000000002E-2</v>
+        <v>6.9709999999999994E-2</v>
       </c>
       <c r="D41">
         <v>53.125</v>
       </c>
       <c r="E41">
-        <v>6.9330000000000003E-2</v>
+        <v>5.314E-2</v>
       </c>
       <c r="F41">
         <v>53.125</v>
       </c>
       <c r="G41">
-        <v>6.9290000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>53.125</v>
@@ -1323,25 +1323,25 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>7.1480000000000002E-2</v>
+        <v>7.1760000000000004E-2</v>
       </c>
       <c r="B42">
         <v>54.6875</v>
       </c>
       <c r="C42">
-        <v>7.1489999999999998E-2</v>
+        <v>7.1749999999999994E-2</v>
       </c>
       <c r="D42">
         <v>54.6875</v>
       </c>
       <c r="E42">
-        <v>7.1370000000000003E-2</v>
+        <v>7.1650000000000005E-2</v>
       </c>
       <c r="F42">
         <v>54.6875</v>
       </c>
       <c r="G42">
-        <v>7.1349999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>54.6875</v>
@@ -1349,25 +1349,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
       <c r="B43">
         <v>56.25</v>
       </c>
       <c r="C43">
-        <v>7.3539999999999994E-2</v>
+        <v>7.3800000000000004E-2</v>
       </c>
       <c r="D43">
         <v>56.25</v>
       </c>
       <c r="E43">
-        <v>7.3419999999999999E-2</v>
+        <v>7.3690000000000005E-2</v>
       </c>
       <c r="F43">
         <v>56.25</v>
       </c>
       <c r="G43">
-        <v>7.3380000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>56.25</v>
@@ -1375,25 +1375,25 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>7.5590000000000004E-2</v>
+        <v>7.5850000000000001E-2</v>
       </c>
       <c r="B44">
         <v>57.8125</v>
       </c>
       <c r="C44">
-        <v>7.5590000000000004E-2</v>
+        <v>7.5850000000000001E-2</v>
       </c>
       <c r="D44">
         <v>57.8125</v>
       </c>
       <c r="E44">
-        <v>7.5459999999999999E-2</v>
+        <v>7.5740000000000002E-2</v>
       </c>
       <c r="F44">
         <v>57.8125</v>
       </c>
       <c r="G44">
-        <v>7.5439999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>57.8125</v>
@@ -1401,25 +1401,25 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>7.7640000000000001E-2</v>
+        <v>7.7909999999999993E-2</v>
       </c>
       <c r="B45">
         <v>59.375</v>
       </c>
       <c r="C45">
-        <v>7.7640000000000001E-2</v>
+        <v>7.7909999999999993E-2</v>
       </c>
       <c r="D45">
         <v>59.375</v>
       </c>
       <c r="E45">
-        <v>7.7499999999999999E-2</v>
+        <v>7.7789999999999998E-2</v>
       </c>
       <c r="F45">
         <v>59.375</v>
       </c>
       <c r="G45">
-        <v>7.7469999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>59.375</v>
@@ -1427,25 +1427,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>7.9680000000000001E-2</v>
+        <v>7.9960000000000003E-2</v>
       </c>
       <c r="B46">
         <v>60.9375</v>
       </c>
       <c r="C46">
-        <v>7.9689999999999997E-2</v>
+        <v>7.9949999999999993E-2</v>
       </c>
       <c r="D46">
         <v>60.9375</v>
       </c>
       <c r="E46">
-        <v>7.9560000000000006E-2</v>
+        <v>7.9829999999999998E-2</v>
       </c>
       <c r="F46">
         <v>60.9375</v>
       </c>
       <c r="G46">
-        <v>7.9519999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>60.9375</v>
@@ -1453,25 +1453,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>8.1720000000000001E-2</v>
+        <v>8.201E-2</v>
       </c>
       <c r="B47">
         <v>62.5</v>
       </c>
       <c r="C47">
-        <v>8.1739999999999993E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="D47">
         <v>62.5</v>
       </c>
       <c r="E47">
-        <v>8.1600000000000006E-2</v>
+        <v>8.1869999999999998E-2</v>
       </c>
       <c r="F47">
         <v>62.5</v>
       </c>
       <c r="G47">
-        <v>8.1570000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>62.5</v>
@@ -1479,25 +1479,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>8.3799999999999999E-2</v>
+        <v>8.4059999999999996E-2</v>
       </c>
       <c r="B48">
         <v>64.0625</v>
       </c>
       <c r="C48">
-        <v>8.3790000000000003E-2</v>
+        <v>8.405E-2</v>
       </c>
       <c r="D48">
         <v>64.0625</v>
       </c>
       <c r="E48">
-        <v>8.3659999999999998E-2</v>
+        <v>8.3909999999999998E-2</v>
       </c>
       <c r="F48">
         <v>64.0625</v>
       </c>
       <c r="G48">
-        <v>8.362E-2</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>64.0625</v>
@@ -1505,25 +1505,25 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>8.5860000000000006E-2</v>
+        <v>8.6120000000000002E-2</v>
       </c>
       <c r="B49">
         <v>65.625</v>
       </c>
       <c r="C49">
-        <v>8.5849999999999996E-2</v>
+        <v>8.6110000000000006E-2</v>
       </c>
       <c r="D49">
         <v>65.625</v>
       </c>
       <c r="E49">
-        <v>8.5709999999999995E-2</v>
+        <v>8.5980000000000001E-2</v>
       </c>
       <c r="F49">
         <v>65.625</v>
       </c>
       <c r="G49">
-        <v>8.5669999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>65.625</v>
@@ -1531,25 +1531,25 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>8.7919999999999998E-2</v>
+        <v>8.8179999999999994E-2</v>
       </c>
       <c r="B50">
         <v>67.1875</v>
       </c>
       <c r="C50">
-        <v>8.7910000000000002E-2</v>
+        <v>8.8160000000000002E-2</v>
       </c>
       <c r="D50">
         <v>67.1875</v>
       </c>
       <c r="E50">
-        <v>8.7770000000000001E-2</v>
+        <v>8.8029999999999997E-2</v>
       </c>
       <c r="F50">
         <v>67.1875</v>
       </c>
       <c r="G50">
-        <v>8.7730000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>67.1875</v>
@@ -1557,522 +1557,522 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>8.9980000000000004E-2</v>
+        <v>9.0230000000000005E-2</v>
       </c>
       <c r="B51">
         <v>68.75</v>
       </c>
       <c r="C51">
-        <v>8.9950000000000002E-2</v>
+        <v>9.0209999999999999E-2</v>
       </c>
       <c r="D51">
         <v>68.75</v>
       </c>
       <c r="E51">
-        <v>8.9819999999999997E-2</v>
+        <v>9.0079999999999993E-2</v>
       </c>
       <c r="F51">
         <v>68.75</v>
       </c>
       <c r="G51">
-        <v>8.9779999999999999E-2</v>
+        <v>9.2020000000000005E-2</v>
       </c>
       <c r="H51">
-        <v>68.75</v>
+        <v>70.3125</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>9.2039999999999997E-2</v>
+        <v>9.2289999999999997E-2</v>
       </c>
       <c r="B52">
         <v>70.3125</v>
       </c>
       <c r="C52">
-        <v>9.2009999999999995E-2</v>
+        <v>9.2270000000000005E-2</v>
       </c>
       <c r="D52">
         <v>70.3125</v>
       </c>
       <c r="E52">
-        <v>9.1880000000000003E-2</v>
+        <v>9.2130000000000004E-2</v>
       </c>
       <c r="F52">
         <v>70.3125</v>
       </c>
       <c r="G52">
-        <v>9.1829999999999995E-2</v>
+        <v>9.4079999999999997E-2</v>
       </c>
       <c r="H52">
-        <v>70.3125</v>
+        <v>71.875</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>9.4100000000000003E-2</v>
+        <v>9.4339999999999993E-2</v>
       </c>
       <c r="B53">
         <v>71.875</v>
       </c>
       <c r="C53">
-        <v>9.4060000000000005E-2</v>
+        <v>9.4329999999999997E-2</v>
       </c>
       <c r="D53">
         <v>71.875</v>
       </c>
       <c r="E53">
-        <v>9.3920000000000003E-2</v>
+        <v>9.4189999999999996E-2</v>
       </c>
       <c r="F53">
         <v>71.875</v>
       </c>
       <c r="G53">
-        <v>9.3869999999999995E-2</v>
+        <v>9.6129999999999993E-2</v>
       </c>
       <c r="H53">
-        <v>71.875</v>
+        <v>73.4375</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>9.6159999999999995E-2</v>
+        <v>9.64E-2</v>
       </c>
       <c r="B54">
         <v>73.4375</v>
       </c>
       <c r="C54">
-        <v>9.6129999999999993E-2</v>
+        <v>9.6390000000000003E-2</v>
       </c>
       <c r="D54">
         <v>73.4375</v>
       </c>
       <c r="E54">
-        <v>9.597E-2</v>
+        <v>9.6240000000000006E-2</v>
       </c>
       <c r="F54">
         <v>73.4375</v>
       </c>
       <c r="G54">
-        <v>9.5930000000000001E-2</v>
+        <v>9.819E-2</v>
       </c>
       <c r="H54">
-        <v>73.4375</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>9.8220000000000002E-2</v>
+        <v>9.8449999999999996E-2</v>
       </c>
       <c r="B55">
         <v>75</v>
       </c>
       <c r="C55">
-        <v>9.819E-2</v>
+        <v>9.844E-2</v>
       </c>
       <c r="D55">
         <v>75</v>
       </c>
       <c r="E55">
-        <v>9.8030000000000006E-2</v>
+        <v>9.8299999999999998E-2</v>
       </c>
       <c r="F55">
         <v>75</v>
       </c>
       <c r="G55">
-        <v>9.7979999999999998E-2</v>
+        <v>0.10024</v>
       </c>
       <c r="H55">
-        <v>75</v>
+        <v>76.5625</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>0.10027999999999999</v>
+        <v>0.10052</v>
       </c>
       <c r="B56">
         <v>76.5625</v>
       </c>
       <c r="C56">
-        <v>0.10024</v>
+        <v>0.10051</v>
       </c>
       <c r="D56">
         <v>76.5625</v>
       </c>
       <c r="E56">
-        <v>0.10008</v>
+        <v>0.10036</v>
       </c>
       <c r="F56">
         <v>76.5625</v>
       </c>
       <c r="G56">
-        <v>0.10004</v>
+        <v>0.10231</v>
       </c>
       <c r="H56">
-        <v>76.5625</v>
+        <v>78.125</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>0.10234</v>
+        <v>0.10259</v>
       </c>
       <c r="B57">
         <v>78.125</v>
       </c>
       <c r="C57">
-        <v>0.1023</v>
+        <v>0.10256999999999999</v>
       </c>
       <c r="D57">
         <v>78.125</v>
       </c>
       <c r="E57">
-        <v>0.10213999999999999</v>
+        <v>0.10242</v>
       </c>
       <c r="F57">
         <v>78.125</v>
       </c>
       <c r="G57">
-        <v>0.10208</v>
+        <v>0.10437</v>
       </c>
       <c r="H57">
-        <v>78.125</v>
+        <v>79.6875</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>0.10442</v>
+        <v>0.10465000000000001</v>
       </c>
       <c r="B58">
         <v>79.6875</v>
       </c>
       <c r="C58">
-        <v>0.10437</v>
+        <v>0.10465000000000001</v>
       </c>
       <c r="D58">
         <v>79.6875</v>
       </c>
       <c r="E58">
-        <v>0.10419</v>
+        <v>0.10448</v>
       </c>
       <c r="F58">
         <v>79.6875</v>
       </c>
       <c r="G58">
-        <v>0.10415000000000001</v>
+        <v>0.10644000000000001</v>
       </c>
       <c r="H58">
-        <v>79.6875</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>0.10647</v>
+        <v>0.10673000000000001</v>
       </c>
       <c r="B59">
         <v>81.25</v>
       </c>
       <c r="C59">
-        <v>0.10643</v>
+        <v>0.10671</v>
       </c>
       <c r="D59">
         <v>81.25</v>
       </c>
       <c r="E59">
-        <v>0.10625</v>
+        <v>0.10654</v>
       </c>
       <c r="F59">
         <v>81.25</v>
       </c>
       <c r="G59">
-        <v>0.10619000000000001</v>
+        <v>0.1085</v>
       </c>
       <c r="H59">
-        <v>81.25</v>
+        <v>82.8125</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>0.10854</v>
+        <v>0.10879</v>
       </c>
       <c r="B60">
         <v>82.8125</v>
       </c>
       <c r="C60">
-        <v>0.10847999999999999</v>
+        <v>0.10876</v>
       </c>
       <c r="D60">
         <v>82.8125</v>
       </c>
       <c r="E60">
-        <v>0.10829999999999999</v>
+        <v>0.10856</v>
       </c>
       <c r="F60">
         <v>82.8125</v>
       </c>
       <c r="G60">
-        <v>0.10825</v>
+        <v>0.11058</v>
       </c>
       <c r="H60">
-        <v>82.8125</v>
+        <v>84.375</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>0.1106</v>
+        <v>0.11088000000000001</v>
       </c>
       <c r="B61">
         <v>84.375</v>
       </c>
       <c r="C61">
-        <v>0.11055</v>
+        <v>0.11083</v>
       </c>
       <c r="D61">
         <v>84.375</v>
       </c>
       <c r="E61">
-        <v>0.11037</v>
+        <v>0.11064</v>
       </c>
       <c r="F61">
         <v>84.375</v>
       </c>
       <c r="G61">
-        <v>0.1103</v>
+        <v>0.11265</v>
       </c>
       <c r="H61">
-        <v>84.375</v>
+        <v>85.9375</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>0.11268</v>
+        <v>0.11296</v>
       </c>
       <c r="B62">
         <v>85.9375</v>
       </c>
       <c r="C62">
-        <v>0.11262999999999999</v>
+        <v>0.11292000000000001</v>
       </c>
       <c r="D62">
         <v>85.9375</v>
       </c>
       <c r="E62">
-        <v>0.11244</v>
+        <v>0.11269999999999999</v>
       </c>
       <c r="F62">
         <v>85.9375</v>
       </c>
       <c r="G62">
-        <v>0.11237</v>
+        <v>0.11473999999999999</v>
       </c>
       <c r="H62">
-        <v>85.9375</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>0.11475</v>
+        <v>0.11505</v>
       </c>
       <c r="B63">
         <v>87.5</v>
       </c>
       <c r="C63">
-        <v>0.11469</v>
+        <v>0.115</v>
       </c>
       <c r="D63">
         <v>87.5</v>
       </c>
       <c r="E63">
-        <v>0.11448999999999999</v>
+        <v>0.11479</v>
       </c>
       <c r="F63">
         <v>87.5</v>
       </c>
       <c r="G63">
-        <v>0.11443</v>
+        <v>0.1168</v>
       </c>
       <c r="H63">
-        <v>87.5</v>
+        <v>89.0625</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>0.11685</v>
+        <v>0.11713</v>
       </c>
       <c r="B64">
         <v>89.0625</v>
       </c>
       <c r="C64">
-        <v>0.11677</v>
+        <v>0.11706999999999999</v>
       </c>
       <c r="D64">
         <v>89.0625</v>
       </c>
       <c r="E64">
-        <v>0.11658</v>
+        <v>0.11687</v>
       </c>
       <c r="F64">
         <v>89.0625</v>
       </c>
       <c r="G64">
-        <v>0.11651</v>
+        <v>0.11888</v>
       </c>
       <c r="H64">
-        <v>89.0625</v>
+        <v>90.625</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.11891</v>
+        <v>0.11921</v>
       </c>
       <c r="B65">
         <v>90.625</v>
       </c>
       <c r="C65">
-        <v>0.11883000000000001</v>
+        <v>0.11916</v>
       </c>
       <c r="D65">
         <v>90.625</v>
       </c>
       <c r="E65">
-        <v>0.11863</v>
+        <v>0.11895</v>
       </c>
       <c r="F65">
         <v>90.625</v>
       </c>
       <c r="G65">
-        <v>0.11856999999999999</v>
+        <v>0.12096</v>
       </c>
       <c r="H65">
-        <v>90.625</v>
+        <v>92.1875</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>0.12099</v>
+        <v>0.12129</v>
       </c>
       <c r="B66">
         <v>92.1875</v>
       </c>
       <c r="C66">
-        <v>0.12091</v>
+        <v>0.12121999999999999</v>
       </c>
       <c r="D66">
         <v>92.1875</v>
       </c>
       <c r="E66">
-        <v>0.12071999999999999</v>
+        <v>0.12101000000000001</v>
       </c>
       <c r="F66">
         <v>92.1875</v>
       </c>
       <c r="G66">
-        <v>0.12064</v>
+        <v>0.12302</v>
       </c>
       <c r="H66">
-        <v>92.1875</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>0.12307</v>
+        <v>0.12338</v>
       </c>
       <c r="B67">
         <v>93.75</v>
       </c>
       <c r="C67">
-        <v>0.123</v>
+        <v>0.12329</v>
       </c>
       <c r="D67">
         <v>93.75</v>
       </c>
       <c r="E67">
-        <v>0.12279</v>
+        <v>0.12309</v>
       </c>
       <c r="F67">
         <v>93.75</v>
       </c>
       <c r="G67">
-        <v>0.12272</v>
+        <v>0.12509000000000001</v>
       </c>
       <c r="H67">
-        <v>93.75</v>
+        <v>95.3125</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.12515999999999999</v>
+        <v>0.12545000000000001</v>
       </c>
       <c r="B68">
         <v>95.3125</v>
       </c>
       <c r="C68">
-        <v>0.12508</v>
+        <v>0.12537000000000001</v>
       </c>
       <c r="D68">
         <v>95.3125</v>
       </c>
       <c r="E68">
-        <v>0.12488</v>
+        <v>0.12515999999999999</v>
       </c>
       <c r="F68">
         <v>95.3125</v>
       </c>
       <c r="G68">
-        <v>0.12479999999999999</v>
+        <v>0.12717000000000001</v>
       </c>
       <c r="H68">
-        <v>95.3125</v>
+        <v>96.875</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>0.12723000000000001</v>
+        <v>0.12751999999999999</v>
       </c>
       <c r="B69">
         <v>96.875</v>
       </c>
       <c r="C69">
-        <v>0.12714</v>
+        <v>0.12744</v>
       </c>
       <c r="D69">
         <v>96.875</v>
       </c>
       <c r="E69">
-        <v>0.12695000000000001</v>
+        <v>0.12723000000000001</v>
       </c>
       <c r="F69">
         <v>96.875</v>
       </c>
       <c r="G69">
-        <v>0.12687000000000001</v>
+        <v>0.12923000000000001</v>
       </c>
       <c r="H69">
-        <v>96.875</v>
+        <v>98.4375</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>0.12931999999999999</v>
+        <v>0.12958</v>
       </c>
       <c r="B70">
         <v>98.4375</v>
       </c>
       <c r="C70">
-        <v>0.12923999999999999</v>
+        <v>0.12950999999999999</v>
       </c>
       <c r="D70">
         <v>98.4375</v>
       </c>
       <c r="E70">
-        <v>0.12903999999999999</v>
+        <v>0.1293</v>
       </c>
       <c r="F70">
         <v>98.4375</v>
       </c>
       <c r="G70">
-        <v>0.12895999999999999</v>
+        <v>0.13102</v>
       </c>
       <c r="H70">
-        <v>98.4375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -2095,527 +2095,527 @@
         <v>100</v>
       </c>
       <c r="G71">
-        <v>0.13102</v>
+        <v>0.12895999999999999</v>
       </c>
       <c r="H71">
-        <v>100</v>
+        <v>98.4375</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>0.12958</v>
+        <v>0.12931999999999999</v>
       </c>
       <c r="B72">
         <v>98.4375</v>
       </c>
       <c r="C72">
-        <v>0.12950999999999999</v>
+        <v>0.12923999999999999</v>
       </c>
       <c r="D72">
         <v>98.4375</v>
       </c>
       <c r="E72">
-        <v>0.1293</v>
+        <v>0.12903999999999999</v>
       </c>
       <c r="F72">
         <v>98.4375</v>
       </c>
       <c r="G72">
-        <v>0.12923000000000001</v>
+        <v>0.12687000000000001</v>
       </c>
       <c r="H72">
-        <v>98.4375</v>
+        <v>96.875</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>0.12751999999999999</v>
+        <v>0.12723000000000001</v>
       </c>
       <c r="B73">
         <v>96.875</v>
       </c>
       <c r="C73">
-        <v>0.12744</v>
+        <v>0.12714</v>
       </c>
       <c r="D73">
         <v>96.875</v>
       </c>
       <c r="E73">
-        <v>0.12723000000000001</v>
+        <v>0.12695000000000001</v>
       </c>
       <c r="F73">
         <v>96.875</v>
       </c>
       <c r="G73">
-        <v>0.12717000000000001</v>
+        <v>0.12479999999999999</v>
       </c>
       <c r="H73">
-        <v>96.875</v>
+        <v>95.3125</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>0.12545000000000001</v>
+        <v>0.12515999999999999</v>
       </c>
       <c r="B74">
         <v>95.3125</v>
       </c>
       <c r="C74">
-        <v>0.12537000000000001</v>
+        <v>0.12508</v>
       </c>
       <c r="D74">
         <v>95.3125</v>
       </c>
       <c r="E74">
-        <v>0.12515999999999999</v>
+        <v>0.12488</v>
       </c>
       <c r="F74">
         <v>95.3125</v>
       </c>
       <c r="G74">
-        <v>0.12509000000000001</v>
+        <v>0.12272</v>
       </c>
       <c r="H74">
-        <v>95.3125</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>0.12338</v>
+        <v>0.12307</v>
       </c>
       <c r="B75">
         <v>93.75</v>
       </c>
       <c r="C75">
-        <v>0.12329</v>
+        <v>0.123</v>
       </c>
       <c r="D75">
         <v>93.75</v>
       </c>
       <c r="E75">
-        <v>0.12309</v>
+        <v>0.12279</v>
       </c>
       <c r="F75">
         <v>93.75</v>
       </c>
       <c r="G75">
-        <v>0.12302</v>
+        <v>0.12064</v>
       </c>
       <c r="H75">
-        <v>93.75</v>
+        <v>92.1875</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>0.12129</v>
+        <v>0.12099</v>
       </c>
       <c r="B76">
         <v>92.1875</v>
       </c>
       <c r="C76">
-        <v>0.12121999999999999</v>
+        <v>0.12091</v>
       </c>
       <c r="D76">
         <v>92.1875</v>
       </c>
       <c r="E76">
-        <v>0.12101000000000001</v>
+        <v>0.12071999999999999</v>
       </c>
       <c r="F76">
         <v>92.1875</v>
       </c>
       <c r="G76">
-        <v>0.12096</v>
+        <v>0.11856999999999999</v>
       </c>
       <c r="H76">
-        <v>92.1875</v>
+        <v>90.625</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>0.11921</v>
+        <v>0.11891</v>
       </c>
       <c r="B77">
         <v>90.625</v>
       </c>
       <c r="C77">
-        <v>0.11916</v>
+        <v>0.11883000000000001</v>
       </c>
       <c r="D77">
         <v>90.625</v>
       </c>
       <c r="E77">
-        <v>0.11895</v>
+        <v>0.11863</v>
       </c>
       <c r="F77">
         <v>90.625</v>
       </c>
       <c r="G77">
-        <v>0.11888</v>
+        <v>0.11651</v>
       </c>
       <c r="H77">
-        <v>90.625</v>
+        <v>89.0625</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>0.11713</v>
+        <v>0.11685</v>
       </c>
       <c r="B78">
         <v>89.0625</v>
       </c>
       <c r="C78">
-        <v>0.11706999999999999</v>
+        <v>0.11677</v>
       </c>
       <c r="D78">
         <v>89.0625</v>
       </c>
       <c r="E78">
-        <v>0.11687</v>
+        <v>0.11658</v>
       </c>
       <c r="F78">
         <v>89.0625</v>
       </c>
       <c r="G78">
-        <v>0.1168</v>
+        <v>0.11443</v>
       </c>
       <c r="H78">
-        <v>89.0625</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>0.11505</v>
+        <v>0.11475</v>
       </c>
       <c r="B79">
         <v>87.5</v>
       </c>
       <c r="C79">
-        <v>0.115</v>
+        <v>0.11469</v>
       </c>
       <c r="D79">
         <v>87.5</v>
       </c>
       <c r="E79">
-        <v>0.11479</v>
+        <v>0.11448999999999999</v>
       </c>
       <c r="F79">
         <v>87.5</v>
       </c>
       <c r="G79">
-        <v>0.11473999999999999</v>
+        <v>0.11237</v>
       </c>
       <c r="H79">
-        <v>87.5</v>
+        <v>85.9375</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>0.11296</v>
+        <v>0.11268</v>
       </c>
       <c r="B80">
         <v>85.9375</v>
       </c>
       <c r="C80">
-        <v>0.11292000000000001</v>
+        <v>0.11262999999999999</v>
       </c>
       <c r="D80">
         <v>85.9375</v>
       </c>
       <c r="E80">
-        <v>0.11269999999999999</v>
+        <v>0.11244</v>
       </c>
       <c r="F80">
         <v>85.9375</v>
       </c>
       <c r="G80">
-        <v>0.11265</v>
+        <v>0.1103</v>
       </c>
       <c r="H80">
-        <v>85.9375</v>
+        <v>84.375</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>0.11088000000000001</v>
+        <v>0.1106</v>
       </c>
       <c r="B81">
         <v>84.375</v>
       </c>
       <c r="C81">
-        <v>0.11083</v>
+        <v>0.11055</v>
       </c>
       <c r="D81">
         <v>84.375</v>
       </c>
       <c r="E81">
-        <v>0.11064</v>
+        <v>0.11037</v>
       </c>
       <c r="F81">
         <v>84.375</v>
       </c>
       <c r="G81">
-        <v>0.11058</v>
+        <v>0.10825</v>
       </c>
       <c r="H81">
-        <v>84.375</v>
+        <v>82.8125</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>0.10879</v>
+        <v>0.10854</v>
       </c>
       <c r="B82">
         <v>82.8125</v>
       </c>
       <c r="C82">
-        <v>0.10876</v>
+        <v>0.10847999999999999</v>
       </c>
       <c r="D82">
         <v>82.8125</v>
       </c>
       <c r="E82">
-        <v>0.10856</v>
+        <v>0.10829999999999999</v>
       </c>
       <c r="F82">
         <v>82.8125</v>
       </c>
       <c r="G82">
-        <v>0.1085</v>
+        <v>0.10619000000000001</v>
       </c>
       <c r="H82">
-        <v>82.8125</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>0.10673000000000001</v>
+        <v>0.10647</v>
       </c>
       <c r="B83">
         <v>81.25</v>
       </c>
       <c r="C83">
-        <v>0.10671</v>
+        <v>0.10643</v>
       </c>
       <c r="D83">
         <v>81.25</v>
       </c>
       <c r="E83">
-        <v>0.10654</v>
+        <v>0.10625</v>
       </c>
       <c r="F83">
         <v>81.25</v>
       </c>
       <c r="G83">
-        <v>0.10644000000000001</v>
+        <v>0.10415000000000001</v>
       </c>
       <c r="H83">
-        <v>81.25</v>
+        <v>79.6875</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>0.10465000000000001</v>
+        <v>0.10442</v>
       </c>
       <c r="B84">
         <v>79.6875</v>
       </c>
       <c r="C84">
-        <v>0.10465000000000001</v>
+        <v>0.10437</v>
       </c>
       <c r="D84">
         <v>79.6875</v>
       </c>
       <c r="E84">
-        <v>0.10448</v>
+        <v>0.10419</v>
       </c>
       <c r="F84">
         <v>79.6875</v>
       </c>
       <c r="G84">
-        <v>0.10437</v>
+        <v>0.10208</v>
       </c>
       <c r="H84">
-        <v>79.6875</v>
+        <v>78.125</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>0.10259</v>
+        <v>0.10234</v>
       </c>
       <c r="B85">
         <v>78.125</v>
       </c>
       <c r="C85">
-        <v>0.10256999999999999</v>
+        <v>0.1023</v>
       </c>
       <c r="D85">
         <v>78.125</v>
       </c>
       <c r="E85">
-        <v>0.10242</v>
+        <v>0.10213999999999999</v>
       </c>
       <c r="F85">
         <v>78.125</v>
       </c>
       <c r="G85">
-        <v>0.10231</v>
+        <v>0.10004</v>
       </c>
       <c r="H85">
-        <v>78.125</v>
+        <v>76.5625</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>0.10052</v>
+        <v>0.10027999999999999</v>
       </c>
       <c r="B86">
         <v>76.5625</v>
       </c>
       <c r="C86">
-        <v>0.10051</v>
+        <v>0.10024</v>
       </c>
       <c r="D86">
         <v>76.5625</v>
       </c>
       <c r="E86">
-        <v>0.10036</v>
+        <v>0.10008</v>
       </c>
       <c r="F86">
         <v>76.5625</v>
       </c>
       <c r="G86">
-        <v>0.10024</v>
+        <v>9.7979999999999998E-2</v>
       </c>
       <c r="H86">
-        <v>76.5625</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>9.8449999999999996E-2</v>
+        <v>9.8220000000000002E-2</v>
       </c>
       <c r="B87">
         <v>75</v>
       </c>
       <c r="C87">
-        <v>9.844E-2</v>
+        <v>9.819E-2</v>
       </c>
       <c r="D87">
         <v>75</v>
       </c>
       <c r="E87">
-        <v>9.8299999999999998E-2</v>
+        <v>9.8030000000000006E-2</v>
       </c>
       <c r="F87">
         <v>75</v>
       </c>
       <c r="G87">
-        <v>9.819E-2</v>
+        <v>9.5930000000000001E-2</v>
       </c>
       <c r="H87">
-        <v>75</v>
+        <v>73.4375</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>9.64E-2</v>
+        <v>9.6159999999999995E-2</v>
       </c>
       <c r="B88">
         <v>73.4375</v>
       </c>
       <c r="C88">
-        <v>9.6390000000000003E-2</v>
+        <v>9.6129999999999993E-2</v>
       </c>
       <c r="D88">
         <v>73.4375</v>
       </c>
       <c r="E88">
-        <v>9.6240000000000006E-2</v>
+        <v>9.597E-2</v>
       </c>
       <c r="F88">
         <v>73.4375</v>
       </c>
       <c r="G88">
-        <v>9.6129999999999993E-2</v>
+        <v>9.3869999999999995E-2</v>
       </c>
       <c r="H88">
-        <v>73.4375</v>
+        <v>71.875</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9.4339999999999993E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="B89">
         <v>71.875</v>
       </c>
       <c r="C89">
-        <v>9.4329999999999997E-2</v>
+        <v>9.4060000000000005E-2</v>
       </c>
       <c r="D89">
         <v>71.875</v>
       </c>
       <c r="E89">
-        <v>9.4189999999999996E-2</v>
+        <v>9.3920000000000003E-2</v>
       </c>
       <c r="F89">
         <v>71.875</v>
       </c>
       <c r="G89">
-        <v>9.4079999999999997E-2</v>
+        <v>9.1829999999999995E-2</v>
       </c>
       <c r="H89">
-        <v>71.875</v>
+        <v>70.3125</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9.2289999999999997E-2</v>
+        <v>9.2039999999999997E-2</v>
       </c>
       <c r="B90">
         <v>70.3125</v>
       </c>
       <c r="C90">
-        <v>9.2270000000000005E-2</v>
+        <v>9.2009999999999995E-2</v>
       </c>
       <c r="D90">
         <v>70.3125</v>
       </c>
       <c r="E90">
-        <v>9.2130000000000004E-2</v>
+        <v>9.1880000000000003E-2</v>
       </c>
       <c r="F90">
         <v>70.3125</v>
       </c>
       <c r="G90">
-        <v>9.2020000000000005E-2</v>
+        <v>8.9779999999999999E-2</v>
       </c>
       <c r="H90">
-        <v>70.3125</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>9.0230000000000005E-2</v>
+        <v>8.9980000000000004E-2</v>
       </c>
       <c r="B91">
         <v>68.75</v>
       </c>
       <c r="C91">
-        <v>9.0209999999999999E-2</v>
+        <v>8.9950000000000002E-2</v>
       </c>
       <c r="D91">
         <v>68.75</v>
       </c>
       <c r="E91">
-        <v>9.0079999999999993E-2</v>
+        <v>8.9819999999999997E-2</v>
       </c>
       <c r="F91">
         <v>68.75</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>8.7730000000000002E-2</v>
       </c>
       <c r="H91">
         <v>67.1875</v>
@@ -2623,25 +2623,25 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>8.8179999999999994E-2</v>
+        <v>8.7919999999999998E-2</v>
       </c>
       <c r="B92">
         <v>67.1875</v>
       </c>
       <c r="C92">
-        <v>8.8160000000000002E-2</v>
+        <v>8.7910000000000002E-2</v>
       </c>
       <c r="D92">
         <v>67.1875</v>
       </c>
       <c r="E92">
-        <v>8.8029999999999997E-2</v>
+        <v>8.7770000000000001E-2</v>
       </c>
       <c r="F92">
         <v>67.1875</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>8.5669999999999996E-2</v>
       </c>
       <c r="H92">
         <v>65.625</v>
@@ -2649,25 +2649,25 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>8.6120000000000002E-2</v>
+        <v>8.5860000000000006E-2</v>
       </c>
       <c r="B93">
         <v>65.625</v>
       </c>
       <c r="C93">
-        <v>8.6110000000000006E-2</v>
+        <v>8.5849999999999996E-2</v>
       </c>
       <c r="D93">
         <v>65.625</v>
       </c>
       <c r="E93">
-        <v>8.5980000000000001E-2</v>
+        <v>8.5709999999999995E-2</v>
       </c>
       <c r="F93">
         <v>65.625</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>8.362E-2</v>
       </c>
       <c r="H93">
         <v>64.0625</v>
@@ -2675,25 +2675,25 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>8.4059999999999996E-2</v>
+        <v>8.3799999999999999E-2</v>
       </c>
       <c r="B94">
         <v>64.0625</v>
       </c>
       <c r="C94">
-        <v>8.405E-2</v>
+        <v>8.3790000000000003E-2</v>
       </c>
       <c r="D94">
         <v>64.0625</v>
       </c>
       <c r="E94">
-        <v>8.3909999999999998E-2</v>
+        <v>8.3659999999999998E-2</v>
       </c>
       <c r="F94">
         <v>64.0625</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>8.1570000000000004E-2</v>
       </c>
       <c r="H94">
         <v>62.5</v>
@@ -2701,25 +2701,25 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>8.201E-2</v>
+        <v>8.1720000000000001E-2</v>
       </c>
       <c r="B95">
         <v>62.5</v>
       </c>
       <c r="C95">
-        <v>8.2000000000000003E-2</v>
+        <v>8.1739999999999993E-2</v>
       </c>
       <c r="D95">
         <v>62.5</v>
       </c>
       <c r="E95">
-        <v>8.1869999999999998E-2</v>
+        <v>8.1600000000000006E-2</v>
       </c>
       <c r="F95">
         <v>62.5</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>7.9519999999999993E-2</v>
       </c>
       <c r="H95">
         <v>60.9375</v>
@@ -2727,25 +2727,25 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>7.9960000000000003E-2</v>
+        <v>7.9680000000000001E-2</v>
       </c>
       <c r="B96">
         <v>60.9375</v>
       </c>
       <c r="C96">
-        <v>7.9949999999999993E-2</v>
+        <v>7.9689999999999997E-2</v>
       </c>
       <c r="D96">
         <v>60.9375</v>
       </c>
       <c r="E96">
-        <v>7.9829999999999998E-2</v>
+        <v>7.9560000000000006E-2</v>
       </c>
       <c r="F96">
         <v>60.9375</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>7.7469999999999997E-2</v>
       </c>
       <c r="H96">
         <v>59.375</v>
@@ -2753,25 +2753,25 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>7.7909999999999993E-2</v>
+        <v>7.7640000000000001E-2</v>
       </c>
       <c r="B97">
         <v>59.375</v>
       </c>
       <c r="C97">
-        <v>7.7909999999999993E-2</v>
+        <v>7.7640000000000001E-2</v>
       </c>
       <c r="D97">
         <v>59.375</v>
       </c>
       <c r="E97">
-        <v>7.7789999999999998E-2</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="F97">
         <v>59.375</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>7.5439999999999993E-2</v>
       </c>
       <c r="H97">
         <v>57.8125</v>
@@ -2779,25 +2779,25 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>7.5850000000000001E-2</v>
+        <v>7.5590000000000004E-2</v>
       </c>
       <c r="B98">
         <v>57.8125</v>
       </c>
       <c r="C98">
-        <v>7.5850000000000001E-2</v>
+        <v>7.5590000000000004E-2</v>
       </c>
       <c r="D98">
         <v>57.8125</v>
       </c>
       <c r="E98">
-        <v>7.5740000000000002E-2</v>
+        <v>7.5459999999999999E-2</v>
       </c>
       <c r="F98">
         <v>57.8125</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>7.3380000000000001E-2</v>
       </c>
       <c r="H98">
         <v>56.25</v>
@@ -2805,25 +2805,25 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>7.3810000000000001E-2</v>
+        <v>7.3539999999999994E-2</v>
       </c>
       <c r="B99">
         <v>56.25</v>
       </c>
       <c r="C99">
-        <v>7.3800000000000004E-2</v>
+        <v>7.3539999999999994E-2</v>
       </c>
       <c r="D99">
         <v>56.25</v>
       </c>
       <c r="E99">
-        <v>7.3690000000000005E-2</v>
+        <v>7.3419999999999999E-2</v>
       </c>
       <c r="F99">
         <v>56.25</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>7.1349999999999997E-2</v>
       </c>
       <c r="H99">
         <v>54.6875</v>
@@ -2831,25 +2831,25 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>7.1760000000000004E-2</v>
+        <v>7.1480000000000002E-2</v>
       </c>
       <c r="B100">
         <v>54.6875</v>
       </c>
       <c r="C100">
-        <v>7.1749999999999994E-2</v>
+        <v>7.1489999999999998E-2</v>
       </c>
       <c r="D100">
         <v>54.6875</v>
       </c>
       <c r="E100">
-        <v>7.1650000000000005E-2</v>
+        <v>7.1370000000000003E-2</v>
       </c>
       <c r="F100">
         <v>54.6875</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>6.9290000000000004E-2</v>
       </c>
       <c r="H100">
         <v>53.125</v>
@@ -2857,25 +2857,25 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>6.9720000000000004E-2</v>
+        <v>6.9430000000000006E-2</v>
       </c>
       <c r="B101">
         <v>53.125</v>
       </c>
       <c r="C101">
-        <v>6.9709999999999994E-2</v>
+        <v>6.9440000000000002E-2</v>
       </c>
       <c r="D101">
         <v>53.125</v>
       </c>
       <c r="E101">
-        <v>5.314E-2</v>
+        <v>6.9330000000000003E-2</v>
       </c>
       <c r="F101">
         <v>53.125</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>6.7250000000000004E-2</v>
       </c>
       <c r="H101">
         <v>51.5625</v>
@@ -2883,25 +2883,25 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>6.7659999999999998E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="B102">
         <v>51.5625</v>
       </c>
       <c r="C102">
-        <v>6.7650000000000002E-2</v>
+        <v>6.7419999999999994E-2</v>
       </c>
       <c r="D102">
         <v>51.5625</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>6.7309999999999995E-2</v>
       </c>
       <c r="F102">
         <v>51.5625</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>6.5140000000000003E-2</v>
       </c>
       <c r="H102">
         <v>50</v>
@@ -2909,25 +2909,25 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>6.5619999999999998E-2</v>
+        <v>6.5269999999999995E-2</v>
       </c>
       <c r="B103">
         <v>50</v>
       </c>
       <c r="C103">
-        <v>6.5619999999999998E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="D103">
         <v>50</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>6.5199999999999994E-2</v>
       </c>
       <c r="F103">
         <v>50</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>6.3109999999999999E-2</v>
       </c>
       <c r="H103">
         <v>48.4375</v>
@@ -2935,25 +2935,25 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>6.3509999999999997E-2</v>
+        <v>6.3229999999999995E-2</v>
       </c>
       <c r="B104">
         <v>48.4375</v>
       </c>
       <c r="C104">
-        <v>6.3500000000000001E-2</v>
+        <v>6.3250000000000001E-2</v>
       </c>
       <c r="D104">
         <v>48.4375</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>6.3149999999999998E-2</v>
       </c>
       <c r="F104">
         <v>48.4375</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>6.105E-2</v>
       </c>
       <c r="H104">
         <v>46.875</v>
@@ -2961,25 +2961,25 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>6.1469999999999997E-2</v>
+        <v>6.1179999999999998E-2</v>
       </c>
       <c r="B105">
         <v>46.875</v>
       </c>
       <c r="C105">
-        <v>6.1460000000000001E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="D105">
         <v>46.875</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>6.1100000000000002E-2</v>
       </c>
       <c r="F105">
         <v>46.875</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>5.901E-2</v>
       </c>
       <c r="H105">
         <v>45.3125</v>
@@ -2987,25 +2987,25 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>5.9409999999999998E-2</v>
+        <v>5.9130000000000002E-2</v>
       </c>
       <c r="B106">
         <v>45.3125</v>
       </c>
       <c r="C106">
-        <v>5.9400000000000001E-2</v>
+        <v>5.9139999999999998E-2</v>
       </c>
       <c r="D106">
         <v>45.3125</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>5.9049999999999998E-2</v>
       </c>
       <c r="F106">
         <v>45.3125</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>5.6980000000000003E-2</v>
       </c>
       <c r="H106">
         <v>43.75</v>
@@ -3013,25 +3013,25 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>5.7369999999999997E-2</v>
+        <v>5.7090000000000002E-2</v>
       </c>
       <c r="B107">
         <v>43.75</v>
       </c>
       <c r="C107">
-        <v>5.7360000000000001E-2</v>
+        <v>5.7110000000000001E-2</v>
       </c>
       <c r="D107">
         <v>43.75</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>5.7009999999999998E-2</v>
       </c>
       <c r="F107">
         <v>43.75</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>5.4940000000000003E-2</v>
       </c>
       <c r="H107">
         <v>42.1875</v>
@@ -3039,25 +3039,25 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>5.5320000000000001E-2</v>
+        <v>5.5050000000000002E-2</v>
       </c>
       <c r="B108">
         <v>42.1875</v>
       </c>
       <c r="C108">
-        <v>5.5320000000000001E-2</v>
+        <v>5.5070000000000001E-2</v>
       </c>
       <c r="D108">
         <v>42.1875</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>5.4980000000000001E-2</v>
       </c>
       <c r="F108">
         <v>42.1875</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>5.289E-2</v>
       </c>
       <c r="H108">
         <v>40.625</v>
@@ -3065,25 +3065,25 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>5.3280000000000001E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="B109">
         <v>40.625</v>
       </c>
       <c r="C109">
-        <v>5.3280000000000001E-2</v>
+        <v>5.3010000000000002E-2</v>
       </c>
       <c r="D109">
         <v>40.625</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>5.2920000000000002E-2</v>
       </c>
       <c r="F109">
         <v>40.625</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>5.0860000000000002E-2</v>
       </c>
       <c r="H109">
         <v>39.0625</v>
@@ -3091,25 +3091,25 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>5.1229999999999998E-2</v>
+        <v>5.0959999999999998E-2</v>
       </c>
       <c r="B110">
         <v>39.0625</v>
       </c>
       <c r="C110">
-        <v>5.1229999999999998E-2</v>
+        <v>5.0970000000000001E-2</v>
       </c>
       <c r="D110">
         <v>39.0625</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>5.0889999999999998E-2</v>
       </c>
       <c r="F110">
         <v>39.0625</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>4.8800000000000003E-2</v>
       </c>
       <c r="H110">
         <v>37.5</v>
@@ -3117,25 +3117,25 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>4.9180000000000001E-2</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="B111">
         <v>37.5</v>
       </c>
       <c r="C111">
-        <v>4.9180000000000001E-2</v>
+        <v>4.8899999999999999E-2</v>
       </c>
       <c r="D111">
         <v>37.5</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>4.8820000000000002E-2</v>
       </c>
       <c r="F111">
         <v>37.5</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>4.6760000000000003E-2</v>
       </c>
       <c r="H111">
         <v>35.9375</v>
@@ -3143,25 +3143,25 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>4.7129999999999998E-2</v>
+        <v>4.6859999999999999E-2</v>
       </c>
       <c r="B112">
         <v>35.9375</v>
       </c>
       <c r="C112">
-        <v>4.7129999999999998E-2</v>
+        <v>4.6870000000000002E-2</v>
       </c>
       <c r="D112">
         <v>35.9375</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>4.6780000000000002E-2</v>
       </c>
       <c r="F112">
         <v>35.9375</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>4.4699999999999997E-2</v>
       </c>
       <c r="H112">
         <v>34.375</v>
@@ -3169,25 +3169,25 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>4.5080000000000002E-2</v>
+        <v>4.48E-2</v>
       </c>
       <c r="B113">
         <v>34.375</v>
       </c>
       <c r="C113">
-        <v>4.5080000000000002E-2</v>
+        <v>4.4819999999999999E-2</v>
       </c>
       <c r="D113">
         <v>34.375</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>4.4729999999999999E-2</v>
       </c>
       <c r="F113">
         <v>34.375</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>4.267E-2</v>
       </c>
       <c r="H113">
         <v>32.8125</v>
@@ -3195,25 +3195,25 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>4.3029999999999999E-2</v>
+        <v>4.2759999999999999E-2</v>
       </c>
       <c r="B114">
         <v>32.8125</v>
       </c>
       <c r="C114">
-        <v>4.3029999999999999E-2</v>
+        <v>4.2770000000000002E-2</v>
       </c>
       <c r="D114">
         <v>32.8125</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>4.2689999999999999E-2</v>
       </c>
       <c r="F114">
         <v>32.8125</v>
       </c>
       <c r="G114" s="1">
-        <v>1.11676E-5</v>
+        <v>4.0640000000000003E-2</v>
       </c>
       <c r="H114">
         <v>31.25</v>
@@ -3221,25 +3221,25 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>4.1000000000000002E-2</v>
+        <v>4.0719999999999999E-2</v>
       </c>
       <c r="B115">
         <v>31.25</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>4.0730000000000002E-2</v>
       </c>
       <c r="D115">
         <v>31.25</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>4.0660000000000002E-2</v>
       </c>
       <c r="F115">
         <v>31.25</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>3.8600000000000002E-2</v>
       </c>
       <c r="H115">
         <v>29.6875</v>
@@ -3247,25 +3247,25 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>3.8949999999999999E-2</v>
+        <v>3.8670000000000003E-2</v>
       </c>
       <c r="B116">
         <v>29.6875</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>3.8699999999999998E-2</v>
       </c>
       <c r="D116">
         <v>29.6875</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>3.8620000000000002E-2</v>
       </c>
       <c r="F116">
         <v>29.6875</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>3.6540000000000003E-2</v>
       </c>
       <c r="H116">
         <v>28.125</v>
@@ -3273,25 +3273,25 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>3.6900000000000002E-2</v>
+        <v>3.662E-2</v>
       </c>
       <c r="B117">
         <v>28.125</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>3.6639999999999999E-2</v>
       </c>
       <c r="D117">
         <v>28.125</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>3.6560000000000002E-2</v>
       </c>
       <c r="F117">
         <v>28.125</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="H117">
         <v>26.5625</v>
@@ -3299,25 +3299,25 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>3.4849999999999999E-2</v>
+        <v>3.4590000000000003E-2</v>
       </c>
       <c r="B118">
         <v>26.5625</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="D118">
         <v>26.5625</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>3.4520000000000002E-2</v>
       </c>
       <c r="F118">
         <v>26.5625</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>3.245E-2</v>
       </c>
       <c r="H118">
         <v>25</v>
@@ -3325,25 +3325,25 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>3.2809999999999999E-2</v>
+        <v>3.2539999999999999E-2</v>
       </c>
       <c r="B119">
         <v>25</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>3.2550000000000003E-2</v>
       </c>
       <c r="D119">
         <v>25</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>3.2489999999999998E-2</v>
       </c>
       <c r="F119">
         <v>25</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>8.8100000000000001E-3</v>
       </c>
       <c r="H119">
         <v>23.4375</v>
@@ -3351,19 +3351,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>3.0769999999999999E-2</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="B120">
         <v>23.4375</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>3.0509999999999999E-2</v>
       </c>
       <c r="D120">
         <v>23.4375</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>3.0439999999999998E-2</v>
       </c>
       <c r="F120">
         <v>23.4375</v>
@@ -3377,19 +3377,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>2.8719999999999999E-2</v>
+        <v>2.844E-2</v>
       </c>
       <c r="B121">
         <v>21.875</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>2.8469999999999999E-2</v>
       </c>
       <c r="D121">
         <v>21.875</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>2.8389999999999999E-2</v>
       </c>
       <c r="F121">
         <v>21.875</v>
@@ -3403,19 +3403,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>2.6669999999999999E-2</v>
+        <v>2.64E-2</v>
       </c>
       <c r="B122">
         <v>20.3125</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>2.6409999999999999E-2</v>
       </c>
       <c r="D122">
         <v>20.3125</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>2.6100000000000002E-2</v>
       </c>
       <c r="F122">
         <v>20.3125</v>
@@ -3429,19 +3429,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>2.462E-2</v>
+        <v>2.436E-2</v>
       </c>
       <c r="B123">
         <v>18.75</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>2.4369999999999999E-2</v>
       </c>
       <c r="D123">
         <v>18.75</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>2.5500000000000002E-3</v>
       </c>
       <c r="F123">
         <v>18.75</v>
@@ -3455,13 +3455,13 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>2.2579999999999999E-2</v>
+        <v>2.231E-2</v>
       </c>
       <c r="B124">
         <v>17.1875</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>2.232E-2</v>
       </c>
       <c r="D124">
         <v>17.1875</v>
@@ -3481,13 +3481,13 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>2.0539999999999999E-2</v>
+        <v>2.026E-2</v>
       </c>
       <c r="B125">
         <v>15.625</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>2.027E-2</v>
       </c>
       <c r="D125">
         <v>15.625</v>
@@ -3507,19 +3507,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>1.848E-2</v>
+        <v>1.823E-2</v>
       </c>
       <c r="B126">
         <v>14.0625</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1.814E-2</v>
       </c>
       <c r="D126">
         <v>14.0625</v>
       </c>
       <c r="E126" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>14.0625</v>
@@ -3533,13 +3533,13 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>1.6389999999999998E-2</v>
+        <v>1.6160000000000001E-2</v>
       </c>
       <c r="B127">
         <v>12.5</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1.423E-2</v>
       </c>
       <c r="D127">
         <v>12.5</v>
@@ -3559,13 +3559,13 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>1.354E-2</v>
+        <v>1.4120000000000001E-2</v>
       </c>
       <c r="B128">
         <v>10.9375</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>7.9699999999999997E-3</v>
       </c>
       <c r="D128">
         <v>10.9375</v>
@@ -3585,13 +3585,13 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>9.5999999999999992E-3</v>
+        <v>1.2030000000000001E-2</v>
       </c>
       <c r="B129">
         <v>9.375</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1.1900000000000001E-3</v>
       </c>
       <c r="D129">
         <v>9.375</v>
@@ -3611,13 +3611,13 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>6.43E-3</v>
+        <v>9.6699999999999998E-3</v>
       </c>
       <c r="B130">
         <v>7.8125</v>
       </c>
-      <c r="C130">
-        <v>0</v>
+      <c r="C130" s="1">
+        <v>3.35028E-5</v>
       </c>
       <c r="D130">
         <v>7.8125</v>
@@ -3637,19 +3637,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>4.0699999999999998E-3</v>
+        <v>7.0699999999999999E-3</v>
       </c>
       <c r="B131">
         <v>6.25</v>
       </c>
-      <c r="C131">
-        <v>0</v>
+      <c r="C131" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D131">
         <v>6.25</v>
       </c>
       <c r="E131" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>6.25</v>
@@ -3663,13 +3663,13 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>2.32E-3</v>
+        <v>4.6699999999999997E-3</v>
       </c>
       <c r="B132">
         <v>4.6875</v>
       </c>
-      <c r="C132">
-        <v>0</v>
+      <c r="C132" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D132">
         <v>4.6875</v>
@@ -3689,13 +3689,13 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>1.1800000000000001E-3</v>
+        <v>2.7200000000000002E-3</v>
       </c>
       <c r="B133">
         <v>3.125</v>
       </c>
-      <c r="C133">
-        <v>0</v>
+      <c r="C133" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="D133">
         <v>3.125</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>4.4670300000000001E-4</v>
+        <v>1.17E-3</v>
       </c>
       <c r="B134">
         <v>1.5625</v>
@@ -3726,8 +3726,8 @@
       <c r="D134">
         <v>1.5625</v>
       </c>
-      <c r="E134">
-        <v>0</v>
+      <c r="E134" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F134">
         <v>1.5625</v>
@@ -3740,8 +3740,8 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>0</v>
+      <c r="A135" s="1">
+        <v>3.35028E-5</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3762,12 +3762,12 @@
         <v>0</v>
       </c>
       <c r="H135">
-        <v>-1.5625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>-1.08E-3</v>
+        <v>-1.2700000000000001E-3</v>
       </c>
       <c r="B136">
         <v>-1.5625</v>
@@ -3778,8 +3778,8 @@
       <c r="D136">
         <v>-1.5625</v>
       </c>
-      <c r="E136">
-        <v>0</v>
+      <c r="E136" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F136">
         <v>-1.5625</v>
@@ -3788,12 +3788,12 @@
         <v>0</v>
       </c>
       <c r="H136">
-        <v>-3.125</v>
+        <v>-1.5625</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>-2.5600000000000002E-3</v>
+        <v>-2.6900000000000001E-3</v>
       </c>
       <c r="B137">
         <v>-3.125</v>
@@ -3804,8 +3804,8 @@
       <c r="D137">
         <v>-3.125</v>
       </c>
-      <c r="E137">
-        <v>0</v>
+      <c r="E137" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F137">
         <v>-3.125</v>
@@ -3814,12 +3814,12 @@
         <v>0</v>
       </c>
       <c r="H137">
-        <v>-4.6875</v>
+        <v>-3.125</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>-4.4000000000000003E-3</v>
+        <v>-4.3600000000000002E-3</v>
       </c>
       <c r="B138">
         <v>-4.6875</v>
@@ -3840,12 +3840,12 @@
         <v>0</v>
       </c>
       <c r="H138">
-        <v>-6.25</v>
+        <v>-4.6875</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>-6.7799999999999996E-3</v>
+        <v>-6.43E-3</v>
       </c>
       <c r="B139">
         <v>-6.25</v>
@@ -3866,18 +3866,18 @@
         <v>0</v>
       </c>
       <c r="H139">
-        <v>-7.8125</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>-9.4699999999999993E-3</v>
+        <v>-9.0699999999999999E-3</v>
       </c>
       <c r="B140">
         <v>-7.8125</v>
       </c>
       <c r="C140" s="1">
-        <v>-7.8173100000000005E-5</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>-7.8125</v>
@@ -3892,18 +3892,18 @@
         <v>0</v>
       </c>
       <c r="H140">
-        <v>-9.375</v>
+        <v>-7.8125</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>-1.197E-2</v>
+        <v>-1.188E-2</v>
       </c>
       <c r="B141">
         <v>-9.375</v>
       </c>
       <c r="C141">
-        <v>-2.0300000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>-9.375</v>
@@ -3918,18 +3918,18 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <v>-10.9375</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>-1.409E-2</v>
+        <v>-1.4319999999999999E-2</v>
       </c>
       <c r="B142">
         <v>-10.9375</v>
       </c>
       <c r="C142">
-        <v>-8.6400000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>-10.9375</v>
@@ -3944,18 +3944,18 @@
         <v>0</v>
       </c>
       <c r="H142">
-        <v>-12.5</v>
+        <v>-10.9375</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>-1.6140000000000002E-2</v>
+        <v>-1.6389999999999998E-2</v>
       </c>
       <c r="B143">
         <v>-12.5</v>
       </c>
       <c r="C143">
-        <v>-1.46E-2</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>-12.5</v>
@@ -3970,24 +3970,24 @@
         <v>0</v>
       </c>
       <c r="H143">
-        <v>-14.0625</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>-1.8200000000000001E-2</v>
+        <v>-1.8460000000000001E-2</v>
       </c>
       <c r="B144">
         <v>-14.0625</v>
       </c>
       <c r="C144">
-        <v>-1.814E-2</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>-14.0625</v>
       </c>
-      <c r="E144">
-        <v>0</v>
+      <c r="E144" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F144">
         <v>-14.0625</v>
@@ -3996,18 +3996,18 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>-15.625</v>
+        <v>-14.0625</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>-2.0250000000000001E-2</v>
+        <v>-2.0490000000000001E-2</v>
       </c>
       <c r="B145">
         <v>-15.625</v>
       </c>
       <c r="C145">
-        <v>-2.0240000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>-15.625</v>
@@ -4022,18 +4022,18 @@
         <v>0</v>
       </c>
       <c r="H145">
-        <v>-17.1875</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>-2.23E-2</v>
+        <v>-2.2550000000000001E-2</v>
       </c>
       <c r="B146">
         <v>-17.1875</v>
       </c>
       <c r="C146">
-        <v>-2.2290000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>-17.1875</v>
@@ -4048,24 +4048,24 @@
         <v>0</v>
       </c>
       <c r="H146">
-        <v>-18.75</v>
+        <v>-17.1875</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>-2.4330000000000001E-2</v>
+        <v>-2.4590000000000001E-2</v>
       </c>
       <c r="B147">
         <v>-18.75</v>
       </c>
       <c r="C147">
-        <v>-2.4330000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>-18.75</v>
       </c>
-      <c r="E147">
-        <v>-5.4200000000000003E-3</v>
+      <c r="E147" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F147">
         <v>-18.75</v>
@@ -4074,24 +4074,24 @@
         <v>0</v>
       </c>
       <c r="H147">
-        <v>-20.3125</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>-2.6380000000000001E-2</v>
+        <v>-2.6630000000000001E-2</v>
       </c>
       <c r="B148">
         <v>-20.3125</v>
       </c>
       <c r="C148">
-        <v>-2.6380000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>-20.3125</v>
       </c>
-      <c r="E148">
-        <v>-2.6280000000000001E-2</v>
+      <c r="E148" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F148">
         <v>-20.3125</v>
@@ -4100,784 +4100,784 @@
         <v>0</v>
       </c>
       <c r="H148">
-        <v>-21.875</v>
+        <v>-20.3125</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>-2.843E-2</v>
+        <v>-2.8680000000000001E-2</v>
       </c>
       <c r="B149">
         <v>-21.875</v>
       </c>
       <c r="C149">
-        <v>-2.843E-2</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>-21.875</v>
       </c>
       <c r="E149">
-        <v>-2.8379999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>-21.875</v>
       </c>
       <c r="G149">
-        <v>-2.4410000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>-23.4375</v>
+        <v>-21.875</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>-3.048E-2</v>
+        <v>-3.073E-2</v>
       </c>
       <c r="B150">
         <v>-23.4375</v>
       </c>
       <c r="C150">
-        <v>-3.048E-2</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>-23.4375</v>
       </c>
       <c r="E150">
-        <v>-3.0429999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>-23.4375</v>
       </c>
       <c r="G150">
-        <v>-3.243E-2</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>-25</v>
+        <v>-23.4375</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>-3.252E-2</v>
+        <v>-3.2779999999999997E-2</v>
       </c>
       <c r="B151">
         <v>-25</v>
       </c>
       <c r="C151">
-        <v>-3.252E-2</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>-25</v>
       </c>
       <c r="E151">
-        <v>-3.2480000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>-25</v>
       </c>
       <c r="G151">
-        <v>-3.4470000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>-26.5625</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>-3.456E-2</v>
+        <v>-3.4819999999999997E-2</v>
       </c>
       <c r="B152">
         <v>-26.5625</v>
       </c>
       <c r="C152">
-        <v>-3.4569999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>-26.5625</v>
       </c>
       <c r="E152">
-        <v>-3.4509999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>-26.5625</v>
       </c>
       <c r="G152">
-        <v>-3.6519999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H152">
-        <v>-28.125</v>
+        <v>-26.5625</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>-3.6609999999999997E-2</v>
+        <v>-3.6859999999999997E-2</v>
       </c>
       <c r="B153">
         <v>-28.125</v>
       </c>
       <c r="C153">
-        <v>-3.6609999999999997E-2</v>
+        <v>-3.6850000000000001E-2</v>
       </c>
       <c r="D153">
         <v>-28.125</v>
       </c>
       <c r="E153">
-        <v>-3.6549999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>-28.125</v>
       </c>
       <c r="G153">
-        <v>-3.857E-2</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>-29.6875</v>
+        <v>-28.125</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>-3.866E-2</v>
+        <v>-3.8920000000000003E-2</v>
       </c>
       <c r="B154">
         <v>-29.6875</v>
       </c>
       <c r="C154">
-        <v>-3.866E-2</v>
+        <v>-3.891E-2</v>
       </c>
       <c r="D154">
         <v>-29.6875</v>
       </c>
       <c r="E154">
-        <v>-3.8609999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>-29.6875</v>
       </c>
       <c r="G154">
-        <v>-4.0620000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>-31.25</v>
+        <v>-29.6875</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>-4.0710000000000003E-2</v>
+        <v>-4.0960000000000003E-2</v>
       </c>
       <c r="B155">
         <v>-31.25</v>
       </c>
       <c r="C155">
-        <v>-4.0719999999999999E-2</v>
+        <v>-4.095E-2</v>
       </c>
       <c r="D155">
         <v>-31.25</v>
       </c>
       <c r="E155">
-        <v>-4.0649999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>-31.25</v>
       </c>
       <c r="G155">
-        <v>-4.265E-2</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>-32.8125</v>
+        <v>-31.25</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>-4.2750000000000003E-2</v>
+        <v>-4.301E-2</v>
       </c>
       <c r="B156">
         <v>-32.8125</v>
       </c>
       <c r="C156">
-        <v>-4.2750000000000003E-2</v>
+        <v>-4.2999999999999997E-2</v>
       </c>
       <c r="D156">
         <v>-32.8125</v>
       </c>
       <c r="E156">
-        <v>-4.2680000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>-32.8125</v>
       </c>
       <c r="G156">
-        <v>-4.4690000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>-34.375</v>
+        <v>-32.8125</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>-4.4790000000000003E-2</v>
+        <v>-4.5039999999999997E-2</v>
       </c>
       <c r="B157">
         <v>-34.375</v>
       </c>
       <c r="C157">
-        <v>-4.4790000000000003E-2</v>
+        <v>-4.5039999999999997E-2</v>
       </c>
       <c r="D157">
         <v>-34.375</v>
       </c>
       <c r="E157">
-        <v>-4.4729999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>-34.375</v>
       </c>
       <c r="G157">
-        <v>-4.6739999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>-35.9375</v>
+        <v>-34.375</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>-4.6850000000000003E-2</v>
+        <v>-4.709E-2</v>
       </c>
       <c r="B158">
         <v>-35.9375</v>
       </c>
       <c r="C158">
-        <v>-4.6829999999999997E-2</v>
+        <v>-4.709E-2</v>
       </c>
       <c r="D158">
         <v>-35.9375</v>
       </c>
       <c r="E158">
-        <v>-4.6760000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>-35.9375</v>
       </c>
       <c r="G158">
-        <v>-4.8779999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>-37.5</v>
+        <v>-35.9375</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>-4.8890000000000003E-2</v>
+        <v>-4.9140000000000003E-2</v>
       </c>
       <c r="B159">
         <v>-37.5</v>
       </c>
       <c r="C159">
-        <v>-4.8869999999999997E-2</v>
+        <v>-4.913E-2</v>
       </c>
       <c r="D159">
         <v>-37.5</v>
       </c>
-      <c r="E159">
-        <v>-4.879E-2</v>
+      <c r="E159" s="1">
+        <v>1.11676E-5</v>
       </c>
       <c r="F159">
         <v>-37.5</v>
       </c>
       <c r="G159">
-        <v>-5.083E-2</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>-39.0625</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>-5.0959999999999998E-2</v>
+        <v>-5.1200000000000002E-2</v>
       </c>
       <c r="B160">
         <v>-39.0625</v>
       </c>
       <c r="C160">
-        <v>-5.0939999999999999E-2</v>
+        <v>-5.1189999999999999E-2</v>
       </c>
       <c r="D160">
         <v>-39.0625</v>
       </c>
       <c r="E160">
-        <v>-5.0860000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>-39.0625</v>
       </c>
       <c r="G160">
-        <v>-5.2880000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>-40.625</v>
+        <v>-39.0625</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>-5.2999999999999999E-2</v>
+        <v>-5.3249999999999999E-2</v>
       </c>
       <c r="B161">
         <v>-40.625</v>
       </c>
       <c r="C161">
-        <v>-5.2979999999999999E-2</v>
+        <v>-5.3240000000000003E-2</v>
       </c>
       <c r="D161">
         <v>-40.625</v>
       </c>
       <c r="E161">
-        <v>-5.2900000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>-40.625</v>
       </c>
       <c r="G161">
-        <v>-5.4919999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>-42.1875</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>-5.5050000000000002E-2</v>
+        <v>-5.5300000000000002E-2</v>
       </c>
       <c r="B162">
         <v>-42.1875</v>
       </c>
       <c r="C162">
-        <v>-5.5030000000000003E-2</v>
+        <v>-5.5289999999999999E-2</v>
       </c>
       <c r="D162">
         <v>-42.1875</v>
       </c>
       <c r="E162">
-        <v>-5.4940000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>-42.1875</v>
       </c>
       <c r="G162">
-        <v>-5.6950000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>-43.75</v>
+        <v>-42.1875</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>-5.7079999999999999E-2</v>
+        <v>-5.7349999999999998E-2</v>
       </c>
       <c r="B163">
         <v>-43.75</v>
       </c>
       <c r="C163">
-        <v>-5.7070000000000003E-2</v>
+        <v>-5.7329999999999999E-2</v>
       </c>
       <c r="D163">
         <v>-43.75</v>
       </c>
       <c r="E163">
-        <v>-5.6980000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>-43.75</v>
       </c>
       <c r="G163">
-        <v>-5.8999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>-45.3125</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>-5.9119999999999999E-2</v>
+        <v>-5.9389999999999998E-2</v>
       </c>
       <c r="B164">
         <v>-45.3125</v>
       </c>
       <c r="C164">
-        <v>-5.9110000000000003E-2</v>
+        <v>-5.9380000000000002E-2</v>
       </c>
       <c r="D164">
         <v>-45.3125</v>
       </c>
       <c r="E164">
-        <v>-5.9020000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>-45.3125</v>
       </c>
       <c r="G164">
-        <v>-6.1039999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>-46.875</v>
+        <v>-45.3125</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>-6.1159999999999999E-2</v>
+        <v>-6.1420000000000002E-2</v>
       </c>
       <c r="B165">
         <v>-46.875</v>
       </c>
       <c r="C165">
-        <v>-6.1150000000000003E-2</v>
+        <v>-6.1420000000000002E-2</v>
       </c>
       <c r="D165">
         <v>-46.875</v>
       </c>
       <c r="E165">
-        <v>-6.1060000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>-46.875</v>
       </c>
       <c r="G165">
-        <v>-6.3089999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>-48.4375</v>
+        <v>-46.875</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>-6.3219999999999998E-2</v>
+        <v>-6.3479999999999995E-2</v>
       </c>
       <c r="B166">
         <v>-48.4375</v>
       </c>
       <c r="C166">
-        <v>-6.3219999999999998E-2</v>
+        <v>-6.3479999999999995E-2</v>
       </c>
       <c r="D166">
         <v>-48.4375</v>
       </c>
       <c r="E166">
-        <v>-6.3119999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>-48.4375</v>
       </c>
       <c r="G166">
-        <v>-6.5129999999999993E-2</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>-50</v>
+        <v>-48.4375</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>-6.5259999999999999E-2</v>
+        <v>-6.5519999999999995E-2</v>
       </c>
       <c r="B167">
         <v>-50</v>
       </c>
       <c r="C167">
-        <v>-6.5259999999999999E-2</v>
+        <v>-6.5519999999999995E-2</v>
       </c>
       <c r="D167">
         <v>-50</v>
       </c>
       <c r="E167">
-        <v>-6.5159999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>-50</v>
       </c>
       <c r="G167">
-        <v>-6.7239999999999994E-2</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>-51.5625</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>-6.7369999999999999E-2</v>
+        <v>-6.7629999999999996E-2</v>
       </c>
       <c r="B168">
         <v>-51.5625</v>
       </c>
       <c r="C168">
-        <v>-6.7390000000000005E-2</v>
+        <v>-6.7629999999999996E-2</v>
       </c>
       <c r="D168">
         <v>-51.5625</v>
       </c>
       <c r="E168">
-        <v>-6.7269999999999996E-2</v>
+        <v>-6.4920000000000005E-2</v>
       </c>
       <c r="F168">
         <v>-51.5625</v>
       </c>
       <c r="G168">
-        <v>-6.9269999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>-53.125</v>
+        <v>-51.5625</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>-6.9419999999999996E-2</v>
+        <v>-6.9669999999999996E-2</v>
       </c>
       <c r="B169">
         <v>-53.125</v>
       </c>
       <c r="C169">
-        <v>-6.9430000000000006E-2</v>
+        <v>-6.9669999999999996E-2</v>
       </c>
       <c r="D169">
         <v>-53.125</v>
       </c>
       <c r="E169">
-        <v>-6.9320000000000007E-2</v>
+        <v>-6.9529999999999995E-2</v>
       </c>
       <c r="F169">
         <v>-53.125</v>
       </c>
       <c r="G169">
-        <v>-7.1330000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>-54.6875</v>
+        <v>-53.125</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>-7.1470000000000006E-2</v>
+        <v>-7.1730000000000002E-2</v>
       </c>
       <c r="B170">
         <v>-54.6875</v>
       </c>
       <c r="C170">
-        <v>-7.1480000000000002E-2</v>
+        <v>-7.1730000000000002E-2</v>
       </c>
       <c r="D170">
         <v>-54.6875</v>
       </c>
       <c r="E170">
-        <v>-7.1370000000000003E-2</v>
+        <v>-7.1569999999999995E-2</v>
       </c>
       <c r="F170">
         <v>-54.6875</v>
       </c>
       <c r="G170">
-        <v>-7.3370000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>-56.25</v>
+        <v>-54.6875</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>-7.3529999999999998E-2</v>
+        <v>-7.3779999999999998E-2</v>
       </c>
       <c r="B171">
         <v>-56.25</v>
       </c>
       <c r="C171">
-        <v>-7.3529999999999998E-2</v>
+        <v>-7.3770000000000002E-2</v>
       </c>
       <c r="D171">
         <v>-56.25</v>
       </c>
       <c r="E171">
-        <v>-7.3429999999999995E-2</v>
+        <v>-7.3620000000000005E-2</v>
       </c>
       <c r="F171">
         <v>-56.25</v>
       </c>
       <c r="G171">
-        <v>-7.5410000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>-57.8125</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>-7.5569999999999998E-2</v>
+        <v>-7.5829999999999995E-2</v>
       </c>
       <c r="B172">
         <v>-57.8125</v>
       </c>
       <c r="C172">
-        <v>-7.5560000000000002E-2</v>
+        <v>-7.5819999999999999E-2</v>
       </c>
       <c r="D172">
         <v>-57.8125</v>
       </c>
       <c r="E172">
-        <v>-7.5459999999999999E-2</v>
+        <v>-7.5660000000000005E-2</v>
       </c>
       <c r="F172">
         <v>-57.8125</v>
       </c>
       <c r="G172">
-        <v>-7.7460000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>-59.375</v>
+        <v>-57.8125</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>-7.7609999999999998E-2</v>
+        <v>-7.7869999999999995E-2</v>
       </c>
       <c r="B173">
         <v>-59.375</v>
       </c>
       <c r="C173">
-        <v>-7.7609999999999998E-2</v>
+        <v>-7.7859999999999999E-2</v>
       </c>
       <c r="D173">
         <v>-59.375</v>
       </c>
       <c r="E173">
-        <v>-7.7499999999999999E-2</v>
+        <v>-7.7700000000000005E-2</v>
       </c>
       <c r="F173">
         <v>-59.375</v>
       </c>
       <c r="G173">
-        <v>-7.9509999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>-60.9375</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>-7.9680000000000001E-2</v>
+        <v>-7.9939999999999997E-2</v>
       </c>
       <c r="B174">
         <v>-60.9375</v>
       </c>
       <c r="C174">
-        <v>-7.9670000000000005E-2</v>
+        <v>-7.9930000000000001E-2</v>
       </c>
       <c r="D174">
         <v>-60.9375</v>
       </c>
       <c r="E174">
-        <v>-7.9560000000000006E-2</v>
+        <v>-7.9759999999999998E-2</v>
       </c>
       <c r="F174">
         <v>-60.9375</v>
       </c>
       <c r="G174">
-        <v>-8.1549999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>-62.5</v>
+        <v>-60.9375</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>-8.1739999999999993E-2</v>
+        <v>-8.1979999999999997E-2</v>
       </c>
       <c r="B175">
         <v>-62.5</v>
       </c>
       <c r="C175">
-        <v>-8.1710000000000005E-2</v>
+        <v>-8.1970000000000001E-2</v>
       </c>
       <c r="D175">
         <v>-62.5</v>
       </c>
       <c r="E175">
-        <v>-8.1600000000000006E-2</v>
+        <v>-8.1799999999999998E-2</v>
       </c>
       <c r="F175">
         <v>-62.5</v>
       </c>
       <c r="G175">
-        <v>-8.3610000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>-64.0625</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>-8.3799999999999999E-2</v>
+        <v>-8.4040000000000004E-2</v>
       </c>
       <c r="B176">
         <v>-64.0625</v>
       </c>
       <c r="C176">
-        <v>-8.3779999999999993E-2</v>
+        <v>-8.4040000000000004E-2</v>
       </c>
       <c r="D176">
         <v>-64.0625</v>
       </c>
       <c r="E176">
-        <v>-8.3669999999999994E-2</v>
+        <v>-8.387E-2</v>
       </c>
       <c r="F176">
         <v>-64.0625</v>
       </c>
       <c r="G176">
-        <v>-8.566E-2</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>-65.625</v>
+        <v>-64.0625</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>-8.5860000000000006E-2</v>
+        <v>-8.609E-2</v>
       </c>
       <c r="B177">
         <v>-65.625</v>
       </c>
       <c r="C177">
-        <v>-8.5830000000000004E-2</v>
+        <v>-8.6080000000000004E-2</v>
       </c>
       <c r="D177">
         <v>-65.625</v>
       </c>
       <c r="E177">
-        <v>-8.5709999999999995E-2</v>
+        <v>-8.591E-2</v>
       </c>
       <c r="F177">
         <v>-65.625</v>
       </c>
       <c r="G177">
-        <v>-8.7720000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>-67.1875</v>
+        <v>-65.625</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>-8.7910000000000002E-2</v>
+        <v>-8.8160000000000002E-2</v>
       </c>
       <c r="B178">
         <v>-67.1875</v>
       </c>
       <c r="C178">
-        <v>-8.7900000000000006E-2</v>
+        <v>-8.8150000000000006E-2</v>
       </c>
       <c r="D178">
         <v>-67.1875</v>
       </c>
       <c r="E178">
-        <v>-8.7779999999999997E-2</v>
+        <v>-8.7970000000000007E-2</v>
       </c>
       <c r="F178">
         <v>-67.1875</v>
       </c>
       <c r="G178">
-        <v>-8.9770000000000003E-2</v>
+        <v>-8.9990000000000001E-2</v>
       </c>
       <c r="H178">
         <v>-68.75</v>
@@ -4885,25 +4885,25 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>-8.9980000000000004E-2</v>
+        <v>-9.0209999999999999E-2</v>
       </c>
       <c r="B179">
         <v>-68.75</v>
       </c>
       <c r="C179">
-        <v>-8.9950000000000002E-2</v>
+        <v>-9.0200000000000002E-2</v>
       </c>
       <c r="D179">
         <v>-68.75</v>
       </c>
       <c r="E179">
-        <v>-8.9819999999999997E-2</v>
+        <v>-9.0020000000000003E-2</v>
       </c>
       <c r="F179">
         <v>-68.75</v>
       </c>
       <c r="G179">
-        <v>-9.1810000000000003E-2</v>
+        <v>-9.2030000000000001E-2</v>
       </c>
       <c r="H179">
         <v>-70.3125</v>
@@ -4911,25 +4911,25 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>-9.2039999999999997E-2</v>
+        <v>-9.2259999999999995E-2</v>
       </c>
       <c r="B180">
         <v>-70.3125</v>
       </c>
       <c r="C180">
-        <v>-9.2009999999999995E-2</v>
+        <v>-9.2259999999999995E-2</v>
       </c>
       <c r="D180">
         <v>-70.3125</v>
       </c>
       <c r="E180">
-        <v>-9.1880000000000003E-2</v>
+        <v>-9.2069999999999999E-2</v>
       </c>
       <c r="F180">
         <v>-70.3125</v>
       </c>
       <c r="G180">
-        <v>-9.3859999999999999E-2</v>
+        <v>-9.4079999999999997E-2</v>
       </c>
       <c r="H180">
         <v>-71.875</v>
@@ -4937,25 +4937,25 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>-9.4100000000000003E-2</v>
+        <v>-9.4310000000000005E-2</v>
       </c>
       <c r="B181">
         <v>-71.875</v>
       </c>
       <c r="C181">
-        <v>-9.4049999999999995E-2</v>
+        <v>-9.4310000000000005E-2</v>
       </c>
       <c r="D181">
         <v>-71.875</v>
       </c>
       <c r="E181">
-        <v>-9.3920000000000003E-2</v>
+        <v>-9.4119999999999995E-2</v>
       </c>
       <c r="F181">
         <v>-71.875</v>
       </c>
       <c r="G181">
-        <v>-9.5920000000000005E-2</v>
+        <v>-9.6140000000000003E-2</v>
       </c>
       <c r="H181">
         <v>-73.4375</v>
@@ -4963,25 +4963,25 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>-9.6159999999999995E-2</v>
+        <v>-9.6379999999999993E-2</v>
       </c>
       <c r="B182">
         <v>-73.4375</v>
       </c>
       <c r="C182">
-        <v>-9.6119999999999997E-2</v>
+        <v>-9.6379999999999993E-2</v>
       </c>
       <c r="D182">
         <v>-73.4375</v>
       </c>
       <c r="E182">
-        <v>-9.597E-2</v>
+        <v>-9.6189999999999998E-2</v>
       </c>
       <c r="F182">
         <v>-73.4375</v>
       </c>
       <c r="G182">
-        <v>-9.7970000000000002E-2</v>
+        <v>-9.8199999999999996E-2</v>
       </c>
       <c r="H182">
         <v>-75</v>
@@ -4989,25 +4989,25 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>-9.8229999999999998E-2</v>
+        <v>-9.8430000000000004E-2</v>
       </c>
       <c r="B183">
         <v>-75</v>
       </c>
       <c r="C183">
-        <v>-9.8169999999999993E-2</v>
+        <v>-9.844E-2</v>
       </c>
       <c r="D183">
         <v>-75</v>
       </c>
       <c r="E183">
-        <v>-9.8030000000000006E-2</v>
+        <v>-9.8239999999999994E-2</v>
       </c>
       <c r="F183">
         <v>-75</v>
       </c>
       <c r="G183">
-        <v>-0.10002999999999999</v>
+        <v>-0.10026</v>
       </c>
       <c r="H183">
         <v>-76.5625</v>
@@ -5015,25 +5015,25 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>-0.10027999999999999</v>
+        <v>-0.10050000000000001</v>
       </c>
       <c r="B184">
         <v>-76.5625</v>
       </c>
       <c r="C184">
-        <v>-0.10023</v>
+        <v>-0.10050000000000001</v>
       </c>
       <c r="D184">
         <v>-76.5625</v>
       </c>
       <c r="E184">
-        <v>-0.10008</v>
+        <v>-0.1003</v>
       </c>
       <c r="F184">
         <v>-76.5625</v>
       </c>
       <c r="G184">
-        <v>-0.10206999999999999</v>
+        <v>-0.10231999999999999</v>
       </c>
       <c r="H184">
         <v>-78.125</v>
@@ -5041,25 +5041,25 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>-0.10235</v>
+        <v>-0.10256</v>
       </c>
       <c r="B185">
         <v>-78.125</v>
       </c>
       <c r="C185">
-        <v>-0.10228</v>
+        <v>-0.10255</v>
       </c>
       <c r="D185">
         <v>-78.125</v>
       </c>
       <c r="E185">
-        <v>-0.10213999999999999</v>
+        <v>-0.10235</v>
       </c>
       <c r="F185">
         <v>-78.125</v>
       </c>
       <c r="G185">
-        <v>-0.10414</v>
+        <v>-0.10439</v>
       </c>
       <c r="H185">
         <v>-79.6875</v>
@@ -5067,25 +5067,25 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>-0.10443</v>
+        <v>-0.10464</v>
       </c>
       <c r="B186">
         <v>-79.6875</v>
       </c>
       <c r="C186">
-        <v>-0.10435999999999999</v>
+        <v>-0.10463</v>
       </c>
       <c r="D186">
         <v>-79.6875</v>
       </c>
       <c r="E186">
-        <v>-0.1042</v>
+        <v>-0.10441</v>
       </c>
       <c r="F186">
         <v>-79.6875</v>
       </c>
       <c r="G186">
-        <v>-0.10619000000000001</v>
+        <v>-0.10646</v>
       </c>
       <c r="H186">
         <v>-81.25</v>
@@ -5093,25 +5093,25 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>-0.10648000000000001</v>
+        <v>-0.1067</v>
       </c>
       <c r="B187">
         <v>-81.25</v>
       </c>
       <c r="C187">
-        <v>-0.10642</v>
+        <v>-0.1067</v>
       </c>
       <c r="D187">
         <v>-81.25</v>
       </c>
       <c r="E187">
-        <v>-0.10625999999999999</v>
+        <v>-0.10647</v>
       </c>
       <c r="F187">
         <v>-81.25</v>
       </c>
       <c r="G187">
-        <v>-0.10824</v>
+        <v>-0.10853</v>
       </c>
       <c r="H187">
         <v>-82.8125</v>
@@ -5119,25 +5119,25 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>-0.10854999999999999</v>
+        <v>-0.10877000000000001</v>
       </c>
       <c r="B188">
         <v>-82.8125</v>
       </c>
       <c r="C188">
-        <v>-0.10847999999999999</v>
+        <v>-0.10877000000000001</v>
       </c>
       <c r="D188">
         <v>-82.8125</v>
       </c>
       <c r="E188">
-        <v>-0.10831</v>
+        <v>-0.10854</v>
       </c>
       <c r="F188">
         <v>-82.8125</v>
       </c>
       <c r="G188">
-        <v>-0.1103</v>
+        <v>-0.11058999999999999</v>
       </c>
       <c r="H188">
         <v>-84.375</v>
@@ -5145,25 +5145,25 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>-0.11061</v>
+        <v>-0.11086</v>
       </c>
       <c r="B189">
         <v>-84.375</v>
       </c>
       <c r="C189">
-        <v>-0.11054</v>
+        <v>-0.11083999999999999</v>
       </c>
       <c r="D189">
         <v>-84.375</v>
       </c>
       <c r="E189">
-        <v>-0.11037</v>
+        <v>-0.1106</v>
       </c>
       <c r="F189">
         <v>-84.375</v>
       </c>
       <c r="G189">
-        <v>-0.11237</v>
+        <v>-0.11268</v>
       </c>
       <c r="H189">
         <v>-85.9375</v>
@@ -5171,25 +5171,25 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>-0.11269999999999999</v>
+        <v>-0.11294999999999999</v>
       </c>
       <c r="B190">
         <v>-85.9375</v>
       </c>
       <c r="C190">
-        <v>-0.11261</v>
+        <v>-0.11292000000000001</v>
       </c>
       <c r="D190">
         <v>-85.9375</v>
       </c>
       <c r="E190">
-        <v>-0.11244999999999999</v>
+        <v>-0.11268</v>
       </c>
       <c r="F190">
         <v>-85.9375</v>
       </c>
       <c r="G190">
-        <v>-0.11445</v>
+        <v>-0.11475</v>
       </c>
       <c r="H190">
         <v>-87.5</v>
@@ -5197,25 +5197,25 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>-0.11477</v>
+        <v>-0.11502999999999999</v>
       </c>
       <c r="B191">
         <v>-87.5</v>
       </c>
       <c r="C191">
-        <v>-0.11468</v>
+        <v>-0.11498999999999999</v>
       </c>
       <c r="D191">
         <v>-87.5</v>
       </c>
       <c r="E191">
-        <v>-0.11451</v>
+        <v>-0.11476</v>
       </c>
       <c r="F191">
         <v>-87.5</v>
       </c>
       <c r="G191">
-        <v>-0.11654</v>
+        <v>-0.11684</v>
       </c>
       <c r="H191">
         <v>-89.0625</v>
@@ -5223,25 +5223,25 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>-0.11686000000000001</v>
+        <v>-0.11713</v>
       </c>
       <c r="B192">
         <v>-89.0625</v>
       </c>
       <c r="C192">
-        <v>-0.11677</v>
+        <v>-0.11708</v>
       </c>
       <c r="D192">
         <v>-89.0625</v>
       </c>
       <c r="E192">
-        <v>-0.11659</v>
+        <v>-0.11685</v>
       </c>
       <c r="F192">
         <v>-89.0625</v>
       </c>
       <c r="G192">
-        <v>-0.1186</v>
+        <v>-0.11890000000000001</v>
       </c>
       <c r="H192">
         <v>-90.625</v>
@@ -5249,25 +5249,25 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>-0.11892</v>
+        <v>-0.1192</v>
       </c>
       <c r="B193">
         <v>-90.625</v>
       </c>
       <c r="C193">
-        <v>-0.11883000000000001</v>
+        <v>-0.11915000000000001</v>
       </c>
       <c r="D193">
         <v>-90.625</v>
       </c>
       <c r="E193">
-        <v>-0.11866</v>
+        <v>-0.11891</v>
       </c>
       <c r="F193">
         <v>-90.625</v>
       </c>
       <c r="G193">
-        <v>-0.12068</v>
+        <v>-0.12098</v>
       </c>
       <c r="H193">
         <v>-92.1875</v>
@@ -5275,25 +5275,25 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>-0.12101000000000001</v>
+        <v>-0.12128</v>
       </c>
       <c r="B194">
         <v>-92.1875</v>
       </c>
       <c r="C194">
-        <v>-0.12091</v>
+        <v>-0.12121999999999999</v>
       </c>
       <c r="D194">
         <v>-92.1875</v>
       </c>
       <c r="E194">
-        <v>-0.12073</v>
+        <v>-0.12099</v>
       </c>
       <c r="F194">
         <v>-92.1875</v>
       </c>
       <c r="G194">
-        <v>-0.12275</v>
+        <v>-0.12304</v>
       </c>
       <c r="H194">
         <v>-93.75</v>
@@ -5301,25 +5301,25 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>-0.12309</v>
+        <v>-0.12336</v>
       </c>
       <c r="B195">
         <v>-93.75</v>
       </c>
       <c r="C195">
-        <v>-0.12299</v>
+        <v>-0.12329</v>
       </c>
       <c r="D195">
         <v>-93.75</v>
       </c>
       <c r="E195">
-        <v>-0.12281</v>
+        <v>-0.12307</v>
       </c>
       <c r="F195">
         <v>-93.75</v>
       </c>
       <c r="G195">
-        <v>-0.12484000000000001</v>
+        <v>-0.12512000000000001</v>
       </c>
       <c r="H195">
         <v>-95.3125</v>
@@ -5327,25 +5327,25 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>-0.12518000000000001</v>
+        <v>-0.12543000000000001</v>
       </c>
       <c r="B196">
         <v>-95.3125</v>
       </c>
       <c r="C196">
-        <v>-0.12508</v>
+        <v>-0.12536</v>
       </c>
       <c r="D196">
         <v>-95.3125</v>
       </c>
       <c r="E196">
-        <v>-0.12489</v>
+        <v>-0.12514</v>
       </c>
       <c r="F196">
         <v>-95.3125</v>
       </c>
       <c r="G196">
-        <v>-0.12691</v>
+        <v>-0.12719</v>
       </c>
       <c r="H196">
         <v>-96.875</v>
@@ -5353,25 +5353,25 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>-0.12726999999999999</v>
+        <v>-0.12751000000000001</v>
       </c>
       <c r="B197">
         <v>-96.875</v>
       </c>
       <c r="C197">
-        <v>-0.12715000000000001</v>
+        <v>-0.12742000000000001</v>
       </c>
       <c r="D197">
         <v>-96.875</v>
       </c>
       <c r="E197">
-        <v>-0.12695999999999999</v>
+        <v>-0.12722</v>
       </c>
       <c r="F197">
         <v>-96.875</v>
       </c>
       <c r="G197">
-        <v>-0.129</v>
+        <v>-0.12925</v>
       </c>
       <c r="H197">
         <v>-98.4375</v>
@@ -5379,19 +5379,19 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>-0.12934999999999999</v>
+        <v>-0.12959999999999999</v>
       </c>
       <c r="B198">
         <v>-98.4375</v>
       </c>
       <c r="C198">
-        <v>-0.12923999999999999</v>
+        <v>-0.1295</v>
       </c>
       <c r="D198">
         <v>-98.4375</v>
       </c>
       <c r="E198">
-        <v>-0.12905</v>
+        <v>-0.1293</v>
       </c>
       <c r="F198">
         <v>-98.4375</v>
@@ -5423,7 +5423,7 @@
         <v>-100</v>
       </c>
       <c r="G199">
-        <v>-0.12925</v>
+        <v>-0.129</v>
       </c>
       <c r="H199">
         <v>-98.4375</v>
@@ -5431,25 +5431,25 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>-0.12959999999999999</v>
+        <v>-0.12934999999999999</v>
       </c>
       <c r="B200">
         <v>-98.4375</v>
       </c>
       <c r="C200">
-        <v>-0.1295</v>
+        <v>-0.12923999999999999</v>
       </c>
       <c r="D200">
         <v>-98.4375</v>
       </c>
       <c r="E200">
-        <v>-0.1293</v>
+        <v>-0.12905</v>
       </c>
       <c r="F200">
         <v>-98.4375</v>
       </c>
       <c r="G200">
-        <v>-0.12719</v>
+        <v>-0.12691</v>
       </c>
       <c r="H200">
         <v>-96.875</v>
@@ -5457,25 +5457,25 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>-0.12751000000000001</v>
+        <v>-0.12726999999999999</v>
       </c>
       <c r="B201">
         <v>-96.875</v>
       </c>
       <c r="C201">
-        <v>-0.12742000000000001</v>
+        <v>-0.12715000000000001</v>
       </c>
       <c r="D201">
         <v>-96.875</v>
       </c>
       <c r="E201">
-        <v>-0.12722</v>
+        <v>-0.12695999999999999</v>
       </c>
       <c r="F201">
         <v>-96.875</v>
       </c>
       <c r="G201">
-        <v>-0.12512000000000001</v>
+        <v>-0.12484000000000001</v>
       </c>
       <c r="H201">
         <v>-95.3125</v>
@@ -5483,25 +5483,25 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>-0.12543000000000001</v>
+        <v>-0.12518000000000001</v>
       </c>
       <c r="B202">
         <v>-95.3125</v>
       </c>
       <c r="C202">
-        <v>-0.12536</v>
+        <v>-0.12508</v>
       </c>
       <c r="D202">
         <v>-95.3125</v>
       </c>
       <c r="E202">
-        <v>-0.12514</v>
+        <v>-0.12489</v>
       </c>
       <c r="F202">
         <v>-95.3125</v>
       </c>
       <c r="G202">
-        <v>-0.12304</v>
+        <v>-0.12275</v>
       </c>
       <c r="H202">
         <v>-93.75</v>
@@ -5509,25 +5509,25 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>-0.12336</v>
+        <v>-0.12309</v>
       </c>
       <c r="B203">
         <v>-93.75</v>
       </c>
       <c r="C203">
-        <v>-0.12329</v>
+        <v>-0.12299</v>
       </c>
       <c r="D203">
         <v>-93.75</v>
       </c>
       <c r="E203">
-        <v>-0.12307</v>
+        <v>-0.12281</v>
       </c>
       <c r="F203">
         <v>-93.75</v>
       </c>
       <c r="G203">
-        <v>-0.12098</v>
+        <v>-0.12068</v>
       </c>
       <c r="H203">
         <v>-92.1875</v>
@@ -5535,25 +5535,25 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>-0.12128</v>
+        <v>-0.12101000000000001</v>
       </c>
       <c r="B204">
         <v>-92.1875</v>
       </c>
       <c r="C204">
-        <v>-0.12121999999999999</v>
+        <v>-0.12091</v>
       </c>
       <c r="D204">
         <v>-92.1875</v>
       </c>
       <c r="E204">
-        <v>-0.12099</v>
+        <v>-0.12073</v>
       </c>
       <c r="F204">
         <v>-92.1875</v>
       </c>
       <c r="G204">
-        <v>-0.11890000000000001</v>
+        <v>-0.1186</v>
       </c>
       <c r="H204">
         <v>-90.625</v>
@@ -5561,25 +5561,25 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>-0.1192</v>
+        <v>-0.11892</v>
       </c>
       <c r="B205">
         <v>-90.625</v>
       </c>
       <c r="C205">
-        <v>-0.11915000000000001</v>
+        <v>-0.11883000000000001</v>
       </c>
       <c r="D205">
         <v>-90.625</v>
       </c>
       <c r="E205">
-        <v>-0.11891</v>
+        <v>-0.11866</v>
       </c>
       <c r="F205">
         <v>-90.625</v>
       </c>
       <c r="G205">
-        <v>-0.11684</v>
+        <v>-0.11654</v>
       </c>
       <c r="H205">
         <v>-89.0625</v>
@@ -5587,25 +5587,25 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>-0.11713</v>
+        <v>-0.11686000000000001</v>
       </c>
       <c r="B206">
         <v>-89.0625</v>
       </c>
       <c r="C206">
-        <v>-0.11708</v>
+        <v>-0.11677</v>
       </c>
       <c r="D206">
         <v>-89.0625</v>
       </c>
       <c r="E206">
-        <v>-0.11685</v>
+        <v>-0.11659</v>
       </c>
       <c r="F206">
         <v>-89.0625</v>
       </c>
       <c r="G206">
-        <v>-0.11475</v>
+        <v>-0.11445</v>
       </c>
       <c r="H206">
         <v>-87.5</v>
@@ -5613,25 +5613,25 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>-0.11502999999999999</v>
+        <v>-0.11477</v>
       </c>
       <c r="B207">
         <v>-87.5</v>
       </c>
       <c r="C207">
-        <v>-0.11498999999999999</v>
+        <v>-0.11468</v>
       </c>
       <c r="D207">
         <v>-87.5</v>
       </c>
       <c r="E207">
-        <v>-0.11476</v>
+        <v>-0.11451</v>
       </c>
       <c r="F207">
         <v>-87.5</v>
       </c>
       <c r="G207">
-        <v>-0.11268</v>
+        <v>-0.11237</v>
       </c>
       <c r="H207">
         <v>-85.9375</v>
@@ -5639,25 +5639,25 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>-0.11294999999999999</v>
+        <v>-0.11269999999999999</v>
       </c>
       <c r="B208">
         <v>-85.9375</v>
       </c>
       <c r="C208">
-        <v>-0.11292000000000001</v>
+        <v>-0.11261</v>
       </c>
       <c r="D208">
         <v>-85.9375</v>
       </c>
       <c r="E208">
-        <v>-0.11268</v>
+        <v>-0.11244999999999999</v>
       </c>
       <c r="F208">
         <v>-85.9375</v>
       </c>
       <c r="G208">
-        <v>-0.11058999999999999</v>
+        <v>-0.1103</v>
       </c>
       <c r="H208">
         <v>-84.375</v>
@@ -5665,25 +5665,25 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>-0.11086</v>
+        <v>-0.11061</v>
       </c>
       <c r="B209">
         <v>-84.375</v>
       </c>
       <c r="C209">
-        <v>-0.11083999999999999</v>
+        <v>-0.11054</v>
       </c>
       <c r="D209">
         <v>-84.375</v>
       </c>
       <c r="E209">
-        <v>-0.1106</v>
+        <v>-0.11037</v>
       </c>
       <c r="F209">
         <v>-84.375</v>
       </c>
       <c r="G209">
-        <v>-0.10853</v>
+        <v>-0.10824</v>
       </c>
       <c r="H209">
         <v>-82.8125</v>
@@ -5691,25 +5691,25 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>-0.10877000000000001</v>
+        <v>-0.10854999999999999</v>
       </c>
       <c r="B210">
         <v>-82.8125</v>
       </c>
       <c r="C210">
-        <v>-0.10877000000000001</v>
+        <v>-0.10847999999999999</v>
       </c>
       <c r="D210">
         <v>-82.8125</v>
       </c>
       <c r="E210">
-        <v>-0.10854</v>
+        <v>-0.10831</v>
       </c>
       <c r="F210">
         <v>-82.8125</v>
       </c>
       <c r="G210">
-        <v>-0.10646</v>
+        <v>-0.10619000000000001</v>
       </c>
       <c r="H210">
         <v>-81.25</v>
@@ -5717,25 +5717,25 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>-0.1067</v>
+        <v>-0.10648000000000001</v>
       </c>
       <c r="B211">
         <v>-81.25</v>
       </c>
       <c r="C211">
-        <v>-0.1067</v>
+        <v>-0.10642</v>
       </c>
       <c r="D211">
         <v>-81.25</v>
       </c>
       <c r="E211">
-        <v>-0.10647</v>
+        <v>-0.10625999999999999</v>
       </c>
       <c r="F211">
         <v>-81.25</v>
       </c>
       <c r="G211">
-        <v>-0.10439</v>
+        <v>-0.10414</v>
       </c>
       <c r="H211">
         <v>-79.6875</v>
@@ -5743,25 +5743,25 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>-0.10464</v>
+        <v>-0.10443</v>
       </c>
       <c r="B212">
         <v>-79.6875</v>
       </c>
       <c r="C212">
-        <v>-0.10463</v>
+        <v>-0.10435999999999999</v>
       </c>
       <c r="D212">
         <v>-79.6875</v>
       </c>
       <c r="E212">
-        <v>-0.10441</v>
+        <v>-0.1042</v>
       </c>
       <c r="F212">
         <v>-79.6875</v>
       </c>
       <c r="G212">
-        <v>-0.10231999999999999</v>
+        <v>-0.10206999999999999</v>
       </c>
       <c r="H212">
         <v>-78.125</v>
@@ -5769,25 +5769,25 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>-0.10256</v>
+        <v>-0.10235</v>
       </c>
       <c r="B213">
         <v>-78.125</v>
       </c>
       <c r="C213">
-        <v>-0.10255</v>
+        <v>-0.10228</v>
       </c>
       <c r="D213">
         <v>-78.125</v>
       </c>
       <c r="E213">
-        <v>-0.10235</v>
+        <v>-0.10213999999999999</v>
       </c>
       <c r="F213">
         <v>-78.125</v>
       </c>
       <c r="G213">
-        <v>-0.10026</v>
+        <v>-0.10002999999999999</v>
       </c>
       <c r="H213">
         <v>-76.5625</v>
@@ -5795,25 +5795,25 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>-0.10050000000000001</v>
+        <v>-0.10027999999999999</v>
       </c>
       <c r="B214">
         <v>-76.5625</v>
       </c>
       <c r="C214">
-        <v>-0.10050000000000001</v>
+        <v>-0.10023</v>
       </c>
       <c r="D214">
         <v>-76.5625</v>
       </c>
       <c r="E214">
-        <v>-0.1003</v>
+        <v>-0.10008</v>
       </c>
       <c r="F214">
         <v>-76.5625</v>
       </c>
       <c r="G214">
-        <v>-9.8199999999999996E-2</v>
+        <v>-9.7970000000000002E-2</v>
       </c>
       <c r="H214">
         <v>-75</v>
@@ -5821,25 +5821,25 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>-9.8430000000000004E-2</v>
+        <v>-9.8229999999999998E-2</v>
       </c>
       <c r="B215">
         <v>-75</v>
       </c>
       <c r="C215">
-        <v>-9.844E-2</v>
+        <v>-9.8169999999999993E-2</v>
       </c>
       <c r="D215">
         <v>-75</v>
       </c>
       <c r="E215">
-        <v>-9.8239999999999994E-2</v>
+        <v>-9.8030000000000006E-2</v>
       </c>
       <c r="F215">
         <v>-75</v>
       </c>
       <c r="G215">
-        <v>-9.6140000000000003E-2</v>
+        <v>-9.5920000000000005E-2</v>
       </c>
       <c r="H215">
         <v>-73.4375</v>
@@ -5847,25 +5847,25 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>-9.6379999999999993E-2</v>
+        <v>-9.6159999999999995E-2</v>
       </c>
       <c r="B216">
         <v>-73.4375</v>
       </c>
       <c r="C216">
-        <v>-9.6379999999999993E-2</v>
+        <v>-9.6119999999999997E-2</v>
       </c>
       <c r="D216">
         <v>-73.4375</v>
       </c>
       <c r="E216">
-        <v>-9.6189999999999998E-2</v>
+        <v>-9.597E-2</v>
       </c>
       <c r="F216">
         <v>-73.4375</v>
       </c>
       <c r="G216">
-        <v>-9.4079999999999997E-2</v>
+        <v>-9.3859999999999999E-2</v>
       </c>
       <c r="H216">
         <v>-71.875</v>
@@ -5873,25 +5873,25 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>-9.4310000000000005E-2</v>
+        <v>-9.4100000000000003E-2</v>
       </c>
       <c r="B217">
         <v>-71.875</v>
       </c>
       <c r="C217">
-        <v>-9.4310000000000005E-2</v>
+        <v>-9.4049999999999995E-2</v>
       </c>
       <c r="D217">
         <v>-71.875</v>
       </c>
       <c r="E217">
-        <v>-9.4119999999999995E-2</v>
+        <v>-9.3920000000000003E-2</v>
       </c>
       <c r="F217">
         <v>-71.875</v>
       </c>
       <c r="G217">
-        <v>-9.2030000000000001E-2</v>
+        <v>-9.1810000000000003E-2</v>
       </c>
       <c r="H217">
         <v>-70.3125</v>
@@ -5899,25 +5899,25 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>-9.2259999999999995E-2</v>
+        <v>-9.2039999999999997E-2</v>
       </c>
       <c r="B218">
         <v>-70.3125</v>
       </c>
       <c r="C218">
-        <v>-9.2259999999999995E-2</v>
+        <v>-9.2009999999999995E-2</v>
       </c>
       <c r="D218">
         <v>-70.3125</v>
       </c>
       <c r="E218">
-        <v>-9.2069999999999999E-2</v>
+        <v>-9.1880000000000003E-2</v>
       </c>
       <c r="F218">
         <v>-70.3125</v>
       </c>
       <c r="G218">
-        <v>-8.9990000000000001E-2</v>
+        <v>-8.9770000000000003E-2</v>
       </c>
       <c r="H218">
         <v>-68.75</v>
@@ -5925,773 +5925,773 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>-9.0209999999999999E-2</v>
+        <v>-8.9980000000000004E-2</v>
       </c>
       <c r="B219">
         <v>-68.75</v>
       </c>
       <c r="C219">
-        <v>-9.0200000000000002E-2</v>
+        <v>-8.9950000000000002E-2</v>
       </c>
       <c r="D219">
         <v>-68.75</v>
       </c>
       <c r="E219">
-        <v>-9.0020000000000003E-2</v>
+        <v>-8.9819999999999997E-2</v>
       </c>
       <c r="F219">
         <v>-68.75</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>-8.7720000000000006E-2</v>
       </c>
       <c r="H219">
-        <v>-65.625</v>
+        <v>-67.1875</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>-8.8160000000000002E-2</v>
+        <v>-8.7910000000000002E-2</v>
       </c>
       <c r="B220">
         <v>-67.1875</v>
       </c>
       <c r="C220">
-        <v>-8.8150000000000006E-2</v>
+        <v>-8.7900000000000006E-2</v>
       </c>
       <c r="D220">
         <v>-67.1875</v>
       </c>
       <c r="E220">
-        <v>-8.7970000000000007E-2</v>
+        <v>-8.7779999999999997E-2</v>
       </c>
       <c r="F220">
         <v>-67.1875</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>-8.566E-2</v>
       </c>
       <c r="H220">
-        <v>-64.0625</v>
+        <v>-65.625</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>-8.609E-2</v>
+        <v>-8.5860000000000006E-2</v>
       </c>
       <c r="B221">
         <v>-65.625</v>
       </c>
       <c r="C221">
-        <v>-8.6080000000000004E-2</v>
+        <v>-8.5830000000000004E-2</v>
       </c>
       <c r="D221">
         <v>-65.625</v>
       </c>
       <c r="E221">
-        <v>-8.591E-2</v>
+        <v>-8.5709999999999995E-2</v>
       </c>
       <c r="F221">
         <v>-65.625</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>-8.3610000000000004E-2</v>
       </c>
       <c r="H221">
-        <v>-62.5</v>
+        <v>-64.0625</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>-8.4040000000000004E-2</v>
+        <v>-8.3799999999999999E-2</v>
       </c>
       <c r="B222">
         <v>-64.0625</v>
       </c>
       <c r="C222">
-        <v>-8.4040000000000004E-2</v>
+        <v>-8.3779999999999993E-2</v>
       </c>
       <c r="D222">
         <v>-64.0625</v>
       </c>
       <c r="E222">
-        <v>-8.387E-2</v>
+        <v>-8.3669999999999994E-2</v>
       </c>
       <c r="F222">
         <v>-64.0625</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>-8.1549999999999997E-2</v>
       </c>
       <c r="H222">
-        <v>-60.9375</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>-8.1979999999999997E-2</v>
+        <v>-8.1739999999999993E-2</v>
       </c>
       <c r="B223">
         <v>-62.5</v>
       </c>
       <c r="C223">
-        <v>-8.1970000000000001E-2</v>
+        <v>-8.1710000000000005E-2</v>
       </c>
       <c r="D223">
         <v>-62.5</v>
       </c>
       <c r="E223">
-        <v>-8.1799999999999998E-2</v>
+        <v>-8.1600000000000006E-2</v>
       </c>
       <c r="F223">
         <v>-62.5</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>-7.9509999999999997E-2</v>
       </c>
       <c r="H223">
-        <v>-59.375</v>
+        <v>-60.9375</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>-7.9939999999999997E-2</v>
+        <v>-7.9680000000000001E-2</v>
       </c>
       <c r="B224">
         <v>-60.9375</v>
       </c>
       <c r="C224">
-        <v>-7.9930000000000001E-2</v>
+        <v>-7.9670000000000005E-2</v>
       </c>
       <c r="D224">
         <v>-60.9375</v>
       </c>
       <c r="E224">
-        <v>-7.9759999999999998E-2</v>
+        <v>-7.9560000000000006E-2</v>
       </c>
       <c r="F224">
         <v>-60.9375</v>
       </c>
       <c r="G224">
-        <v>0</v>
+        <v>-7.7460000000000001E-2</v>
       </c>
       <c r="H224">
-        <v>-57.8125</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>-7.7869999999999995E-2</v>
+        <v>-7.7609999999999998E-2</v>
       </c>
       <c r="B225">
         <v>-59.375</v>
       </c>
       <c r="C225">
-        <v>-7.7859999999999999E-2</v>
+        <v>-7.7609999999999998E-2</v>
       </c>
       <c r="D225">
         <v>-59.375</v>
       </c>
       <c r="E225">
-        <v>-7.7700000000000005E-2</v>
+        <v>-7.7499999999999999E-2</v>
       </c>
       <c r="F225">
         <v>-59.375</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>-7.5410000000000005E-2</v>
       </c>
       <c r="H225">
-        <v>-56.25</v>
+        <v>-57.8125</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>-7.5829999999999995E-2</v>
+        <v>-7.5569999999999998E-2</v>
       </c>
       <c r="B226">
         <v>-57.8125</v>
       </c>
       <c r="C226">
-        <v>-7.5819999999999999E-2</v>
+        <v>-7.5560000000000002E-2</v>
       </c>
       <c r="D226">
         <v>-57.8125</v>
       </c>
       <c r="E226">
-        <v>-7.5660000000000005E-2</v>
+        <v>-7.5459999999999999E-2</v>
       </c>
       <c r="F226">
         <v>-57.8125</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>-7.3370000000000005E-2</v>
       </c>
       <c r="H226">
-        <v>-54.6875</v>
+        <v>-56.25</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>-7.3779999999999998E-2</v>
+        <v>-7.3529999999999998E-2</v>
       </c>
       <c r="B227">
         <v>-56.25</v>
       </c>
       <c r="C227">
-        <v>-7.3770000000000002E-2</v>
+        <v>-7.3529999999999998E-2</v>
       </c>
       <c r="D227">
         <v>-56.25</v>
       </c>
       <c r="E227">
-        <v>-7.3620000000000005E-2</v>
+        <v>-7.3429999999999995E-2</v>
       </c>
       <c r="F227">
         <v>-56.25</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>-7.1330000000000005E-2</v>
       </c>
       <c r="H227">
-        <v>-53.125</v>
+        <v>-54.6875</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>-7.1730000000000002E-2</v>
+        <v>-7.1470000000000006E-2</v>
       </c>
       <c r="B228">
         <v>-54.6875</v>
       </c>
       <c r="C228">
-        <v>-7.1730000000000002E-2</v>
+        <v>-7.1480000000000002E-2</v>
       </c>
       <c r="D228">
         <v>-54.6875</v>
       </c>
       <c r="E228">
-        <v>-7.1569999999999995E-2</v>
+        <v>-7.1370000000000003E-2</v>
       </c>
       <c r="F228">
         <v>-54.6875</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>-6.9269999999999998E-2</v>
       </c>
       <c r="H228">
-        <v>-51.5625</v>
+        <v>-53.125</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>-6.9669999999999996E-2</v>
+        <v>-6.9419999999999996E-2</v>
       </c>
       <c r="B229">
         <v>-53.125</v>
       </c>
       <c r="C229">
-        <v>-6.9669999999999996E-2</v>
+        <v>-6.9430000000000006E-2</v>
       </c>
       <c r="D229">
         <v>-53.125</v>
       </c>
       <c r="E229">
-        <v>-6.9529999999999995E-2</v>
+        <v>-6.9320000000000007E-2</v>
       </c>
       <c r="F229">
         <v>-53.125</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>-6.7239999999999994E-2</v>
       </c>
       <c r="H229">
-        <v>-50</v>
+        <v>-51.5625</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>-6.7629999999999996E-2</v>
+        <v>-6.7369999999999999E-2</v>
       </c>
       <c r="B230">
         <v>-51.5625</v>
       </c>
       <c r="C230">
-        <v>-6.7629999999999996E-2</v>
+        <v>-6.7390000000000005E-2</v>
       </c>
       <c r="D230">
         <v>-51.5625</v>
       </c>
       <c r="E230">
-        <v>-6.4920000000000005E-2</v>
+        <v>-6.7269999999999996E-2</v>
       </c>
       <c r="F230">
         <v>-51.5625</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>-6.5129999999999993E-2</v>
       </c>
       <c r="H230">
-        <v>-48.4375</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>-6.5519999999999995E-2</v>
+        <v>-6.5259999999999999E-2</v>
       </c>
       <c r="B231">
         <v>-50</v>
       </c>
       <c r="C231">
-        <v>-6.5519999999999995E-2</v>
+        <v>-6.5259999999999999E-2</v>
       </c>
       <c r="D231">
         <v>-50</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>-6.5159999999999996E-2</v>
       </c>
       <c r="F231">
         <v>-50</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>-6.3089999999999993E-2</v>
       </c>
       <c r="H231">
-        <v>-46.875</v>
+        <v>-48.4375</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>-6.3479999999999995E-2</v>
+        <v>-6.3219999999999998E-2</v>
       </c>
       <c r="B232">
         <v>-48.4375</v>
       </c>
       <c r="C232">
-        <v>-6.3479999999999995E-2</v>
+        <v>-6.3219999999999998E-2</v>
       </c>
       <c r="D232">
         <v>-48.4375</v>
       </c>
       <c r="E232">
-        <v>0</v>
+        <v>-6.3119999999999996E-2</v>
       </c>
       <c r="F232">
         <v>-48.4375</v>
       </c>
       <c r="G232">
-        <v>0</v>
+        <v>-6.1039999999999997E-2</v>
       </c>
       <c r="H232">
-        <v>-45.3125</v>
+        <v>-46.875</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>-6.1420000000000002E-2</v>
+        <v>-6.1159999999999999E-2</v>
       </c>
       <c r="B233">
         <v>-46.875</v>
       </c>
       <c r="C233">
-        <v>-6.1420000000000002E-2</v>
+        <v>-6.1150000000000003E-2</v>
       </c>
       <c r="D233">
         <v>-46.875</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>-6.1060000000000003E-2</v>
       </c>
       <c r="F233">
         <v>-46.875</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>-5.8999999999999997E-2</v>
       </c>
       <c r="H233">
-        <v>-43.75</v>
+        <v>-45.3125</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>-5.9389999999999998E-2</v>
+        <v>-5.9119999999999999E-2</v>
       </c>
       <c r="B234">
         <v>-45.3125</v>
       </c>
       <c r="C234">
-        <v>-5.9380000000000002E-2</v>
+        <v>-5.9110000000000003E-2</v>
       </c>
       <c r="D234">
         <v>-45.3125</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>-5.9020000000000003E-2</v>
       </c>
       <c r="F234">
         <v>-45.3125</v>
       </c>
       <c r="G234">
-        <v>0</v>
+        <v>-5.6950000000000001E-2</v>
       </c>
       <c r="H234">
-        <v>-42.1875</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>-5.7349999999999998E-2</v>
+        <v>-5.7079999999999999E-2</v>
       </c>
       <c r="B235">
         <v>-43.75</v>
       </c>
       <c r="C235">
-        <v>-5.7329999999999999E-2</v>
+        <v>-5.7070000000000003E-2</v>
       </c>
       <c r="D235">
         <v>-43.75</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>-5.6980000000000003E-2</v>
       </c>
       <c r="F235">
         <v>-43.75</v>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>-5.4919999999999997E-2</v>
       </c>
       <c r="H235">
-        <v>-40.625</v>
+        <v>-42.1875</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>-5.5300000000000002E-2</v>
+        <v>-5.5050000000000002E-2</v>
       </c>
       <c r="B236">
         <v>-42.1875</v>
       </c>
       <c r="C236">
-        <v>-5.5289999999999999E-2</v>
+        <v>-5.5030000000000003E-2</v>
       </c>
       <c r="D236">
         <v>-42.1875</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>-5.4940000000000003E-2</v>
       </c>
       <c r="F236">
         <v>-42.1875</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>-5.2880000000000003E-2</v>
       </c>
       <c r="H236">
-        <v>-39.0625</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>-5.3249999999999999E-2</v>
+        <v>-5.2999999999999999E-2</v>
       </c>
       <c r="B237">
         <v>-40.625</v>
       </c>
       <c r="C237">
-        <v>-5.3240000000000003E-2</v>
+        <v>-5.2979999999999999E-2</v>
       </c>
       <c r="D237">
         <v>-40.625</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>-5.2900000000000003E-2</v>
       </c>
       <c r="F237">
         <v>-40.625</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>-5.083E-2</v>
       </c>
       <c r="H237">
-        <v>-37.5</v>
+        <v>-39.0625</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>-5.1200000000000002E-2</v>
+        <v>-5.0959999999999998E-2</v>
       </c>
       <c r="B238">
         <v>-39.0625</v>
       </c>
       <c r="C238">
-        <v>-5.1189999999999999E-2</v>
+        <v>-5.0939999999999999E-2</v>
       </c>
       <c r="D238">
         <v>-39.0625</v>
       </c>
       <c r="E238">
-        <v>0</v>
+        <v>-5.0860000000000002E-2</v>
       </c>
       <c r="F238">
         <v>-39.0625</v>
       </c>
       <c r="G238">
-        <v>0</v>
+        <v>-4.8779999999999997E-2</v>
       </c>
       <c r="H238">
-        <v>-35.9375</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>-4.9140000000000003E-2</v>
+        <v>-4.8890000000000003E-2</v>
       </c>
       <c r="B239">
         <v>-37.5</v>
       </c>
       <c r="C239">
-        <v>-4.913E-2</v>
+        <v>-4.8869999999999997E-2</v>
       </c>
       <c r="D239">
         <v>-37.5</v>
       </c>
       <c r="E239" s="1">
-        <v>1.11676E-5</v>
+        <v>-4.879E-2</v>
       </c>
       <c r="F239">
         <v>-37.5</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>-4.6739999999999997E-2</v>
       </c>
       <c r="H239">
-        <v>-34.375</v>
+        <v>-35.9375</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>-4.709E-2</v>
+        <v>-4.6850000000000003E-2</v>
       </c>
       <c r="B240">
         <v>-35.9375</v>
       </c>
       <c r="C240">
-        <v>-4.709E-2</v>
+        <v>-4.6829999999999997E-2</v>
       </c>
       <c r="D240">
         <v>-35.9375</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>-4.6760000000000003E-2</v>
       </c>
       <c r="F240">
         <v>-35.9375</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>-4.4690000000000001E-2</v>
       </c>
       <c r="H240">
-        <v>-32.8125</v>
+        <v>-34.375</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>-4.5039999999999997E-2</v>
+        <v>-4.4790000000000003E-2</v>
       </c>
       <c r="B241">
         <v>-34.375</v>
       </c>
       <c r="C241">
-        <v>-4.5039999999999997E-2</v>
+        <v>-4.4790000000000003E-2</v>
       </c>
       <c r="D241">
         <v>-34.375</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>-4.4729999999999999E-2</v>
       </c>
       <c r="F241">
         <v>-34.375</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>-4.265E-2</v>
       </c>
       <c r="H241">
-        <v>-31.25</v>
+        <v>-32.8125</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>-4.301E-2</v>
+        <v>-4.2750000000000003E-2</v>
       </c>
       <c r="B242">
         <v>-32.8125</v>
       </c>
       <c r="C242">
-        <v>-4.2999999999999997E-2</v>
+        <v>-4.2750000000000003E-2</v>
       </c>
       <c r="D242">
         <v>-32.8125</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>-4.2680000000000003E-2</v>
       </c>
       <c r="F242">
         <v>-32.8125</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>-4.0620000000000003E-2</v>
       </c>
       <c r="H242">
-        <v>-29.6875</v>
+        <v>-31.25</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>-4.0960000000000003E-2</v>
+        <v>-4.0710000000000003E-2</v>
       </c>
       <c r="B243">
         <v>-31.25</v>
       </c>
       <c r="C243">
-        <v>-4.095E-2</v>
+        <v>-4.0719999999999999E-2</v>
       </c>
       <c r="D243">
         <v>-31.25</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>-4.0649999999999999E-2</v>
       </c>
       <c r="F243">
         <v>-31.25</v>
       </c>
       <c r="G243">
-        <v>0</v>
+        <v>-3.857E-2</v>
       </c>
       <c r="H243">
-        <v>-28.125</v>
+        <v>-29.6875</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>-3.8920000000000003E-2</v>
+        <v>-3.866E-2</v>
       </c>
       <c r="B244">
         <v>-29.6875</v>
       </c>
       <c r="C244">
-        <v>-3.891E-2</v>
+        <v>-3.866E-2</v>
       </c>
       <c r="D244">
         <v>-29.6875</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>-3.8609999999999998E-2</v>
       </c>
       <c r="F244">
         <v>-29.6875</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>-3.6519999999999997E-2</v>
       </c>
       <c r="H244">
-        <v>-26.5625</v>
+        <v>-28.125</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>-3.6859999999999997E-2</v>
+        <v>-3.6609999999999997E-2</v>
       </c>
       <c r="B245">
         <v>-28.125</v>
       </c>
       <c r="C245">
-        <v>-3.6850000000000001E-2</v>
+        <v>-3.6609999999999997E-2</v>
       </c>
       <c r="D245">
         <v>-28.125</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>-3.6549999999999999E-2</v>
       </c>
       <c r="F245">
         <v>-28.125</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>-3.4470000000000001E-2</v>
       </c>
       <c r="H245">
-        <v>-25</v>
+        <v>-26.5625</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>-3.4819999999999997E-2</v>
+        <v>-3.456E-2</v>
       </c>
       <c r="B246">
         <v>-26.5625</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>-3.4569999999999997E-2</v>
       </c>
       <c r="D246">
         <v>-26.5625</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>-3.4509999999999999E-2</v>
       </c>
       <c r="F246">
         <v>-26.5625</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>-3.243E-2</v>
       </c>
       <c r="H246">
-        <v>-23.4375</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>-3.2779999999999997E-2</v>
+        <v>-3.252E-2</v>
       </c>
       <c r="B247">
         <v>-25</v>
       </c>
       <c r="C247">
-        <v>0</v>
+        <v>-3.252E-2</v>
       </c>
       <c r="D247">
         <v>-25</v>
       </c>
       <c r="E247">
-        <v>0</v>
+        <v>-3.2480000000000002E-2</v>
       </c>
       <c r="F247">
         <v>-25</v>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>-2.4410000000000001E-2</v>
       </c>
       <c r="H247">
-        <v>-21.875</v>
+        <v>-23.4375</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>-3.073E-2</v>
+        <v>-3.048E-2</v>
       </c>
       <c r="B248">
         <v>-23.4375</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>-3.048E-2</v>
       </c>
       <c r="D248">
         <v>-23.4375</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>-3.0429999999999999E-2</v>
       </c>
       <c r="F248">
         <v>-23.4375</v>
@@ -6700,24 +6700,24 @@
         <v>0</v>
       </c>
       <c r="H248">
-        <v>-20.3125</v>
+        <v>-21.875</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>-2.8680000000000001E-2</v>
+        <v>-2.843E-2</v>
       </c>
       <c r="B249">
         <v>-21.875</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>-2.843E-2</v>
       </c>
       <c r="D249">
         <v>-21.875</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>-2.8379999999999999E-2</v>
       </c>
       <c r="F249">
         <v>-21.875</v>
@@ -6726,24 +6726,24 @@
         <v>0</v>
       </c>
       <c r="H249">
-        <v>-18.75</v>
+        <v>-20.3125</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>-2.6630000000000001E-2</v>
+        <v>-2.6380000000000001E-2</v>
       </c>
       <c r="B250">
         <v>-20.3125</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>-2.6380000000000001E-2</v>
       </c>
       <c r="D250">
         <v>-20.3125</v>
       </c>
       <c r="E250" s="1">
-        <v>1.11676E-5</v>
+        <v>-2.6280000000000001E-2</v>
       </c>
       <c r="F250">
         <v>-20.3125</v>
@@ -6752,24 +6752,24 @@
         <v>0</v>
       </c>
       <c r="H250">
-        <v>-17.1875</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>-2.4590000000000001E-2</v>
+        <v>-2.4330000000000001E-2</v>
       </c>
       <c r="B251">
         <v>-18.75</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>-2.4330000000000001E-2</v>
       </c>
       <c r="D251">
         <v>-18.75</v>
       </c>
       <c r="E251" s="1">
-        <v>1.11676E-5</v>
+        <v>-5.4200000000000003E-3</v>
       </c>
       <c r="F251">
         <v>-18.75</v>
@@ -6778,18 +6778,18 @@
         <v>0</v>
       </c>
       <c r="H251">
-        <v>-15.625</v>
+        <v>-17.1875</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>-2.2550000000000001E-2</v>
+        <v>-2.23E-2</v>
       </c>
       <c r="B252">
         <v>-17.1875</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>-2.2290000000000001E-2</v>
       </c>
       <c r="D252">
         <v>-17.1875</v>
@@ -6804,18 +6804,18 @@
         <v>0</v>
       </c>
       <c r="H252">
-        <v>-14.0625</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>-2.0490000000000001E-2</v>
+        <v>-2.0250000000000001E-2</v>
       </c>
       <c r="B253">
         <v>-15.625</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>-2.0240000000000001E-2</v>
       </c>
       <c r="D253">
         <v>-15.625</v>
@@ -6830,24 +6830,24 @@
         <v>0</v>
       </c>
       <c r="H253">
-        <v>-12.5</v>
+        <v>-14.0625</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>-1.8460000000000001E-2</v>
+        <v>-1.8200000000000001E-2</v>
       </c>
       <c r="B254">
         <v>-14.0625</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>-1.814E-2</v>
       </c>
       <c r="D254">
         <v>-14.0625</v>
       </c>
       <c r="E254" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F254">
         <v>-14.0625</v>
@@ -6856,18 +6856,18 @@
         <v>0</v>
       </c>
       <c r="H254">
-        <v>-10.9375</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>-1.6389999999999998E-2</v>
+        <v>-1.6140000000000002E-2</v>
       </c>
       <c r="B255">
         <v>-12.5</v>
       </c>
       <c r="C255">
-        <v>0</v>
+        <v>-1.46E-2</v>
       </c>
       <c r="D255">
         <v>-12.5</v>
@@ -6882,18 +6882,18 @@
         <v>0</v>
       </c>
       <c r="H255">
-        <v>-9.375</v>
+        <v>-10.9375</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>-1.4319999999999999E-2</v>
+        <v>-1.409E-2</v>
       </c>
       <c r="B256">
         <v>-10.9375</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>-8.6400000000000001E-3</v>
       </c>
       <c r="D256">
         <v>-10.9375</v>
@@ -6908,18 +6908,18 @@
         <v>0</v>
       </c>
       <c r="H256">
-        <v>-7.8125</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>-1.188E-2</v>
+        <v>-1.197E-2</v>
       </c>
       <c r="B257">
         <v>-9.375</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>-2.0300000000000001E-3</v>
       </c>
       <c r="D257">
         <v>-9.375</v>
@@ -6934,18 +6934,18 @@
         <v>0</v>
       </c>
       <c r="H257">
-        <v>-6.25</v>
+        <v>-7.8125</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>-9.0699999999999999E-3</v>
+        <v>-9.4699999999999993E-3</v>
       </c>
       <c r="B258">
         <v>-7.8125</v>
       </c>
-      <c r="C258">
-        <v>0</v>
+      <c r="C258" s="1">
+        <v>-7.8173100000000005E-5</v>
       </c>
       <c r="D258">
         <v>-7.8125</v>
@@ -6960,12 +6960,12 @@
         <v>0</v>
       </c>
       <c r="H258">
-        <v>-4.6875</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>-6.43E-3</v>
+        <v>-6.7799999999999996E-3</v>
       </c>
       <c r="B259">
         <v>-6.25</v>
@@ -6986,12 +6986,12 @@
         <v>0</v>
       </c>
       <c r="H259">
-        <v>-3.125</v>
+        <v>-4.6875</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>-4.3600000000000002E-3</v>
+        <v>-4.4000000000000003E-3</v>
       </c>
       <c r="B260">
         <v>-4.6875</v>
@@ -7012,12 +7012,12 @@
         <v>0</v>
       </c>
       <c r="H260">
-        <v>-1.5625</v>
+        <v>-3.125</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>-2.6900000000000001E-3</v>
+        <v>-2.5600000000000002E-3</v>
       </c>
       <c r="B261">
         <v>-3.125</v>
@@ -7029,7 +7029,7 @@
         <v>-3.125</v>
       </c>
       <c r="E261" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F261">
         <v>-3.125</v>
@@ -7038,12 +7038,12 @@
         <v>0</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>-1.5625</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>-1.2700000000000001E-3</v>
+        <v>-1.08E-3</v>
       </c>
       <c r="B262">
         <v>-1.5625</v>
@@ -7055,7 +7055,7 @@
         <v>-1.5625</v>
       </c>
       <c r="E262" s="1">
-        <v>1.11676E-5</v>
+        <v>0</v>
       </c>
       <c r="F262">
         <v>-1.5625</v>
